--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45303</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44239</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>44393</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>44474</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45434</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44284</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45525</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45530</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>45585</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45468</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45473</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45671</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45551</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44505</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45604</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>45638</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45686</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44795</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45502</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>44539</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44497</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>45237</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45473</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>44994</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45551</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45686</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>44935</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>45677</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45204</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45608</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>45691</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45335</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>44120</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44868</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45730</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>45473</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45475</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45505</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44931</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45671</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45502</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45475</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>45761</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>44896</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>45463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45425</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45363</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>45232</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>45635</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45722</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45274</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45435</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44342</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45811</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>45834</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44398</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>45301</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>45699</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45253</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44249</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45196</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44931</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45180</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44887</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45686</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45611</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45471</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45548</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>45604</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45411</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45671</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45671</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45000</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45737</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45314</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45834</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44064</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45673</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45238</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45321</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45135</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44848</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>45743.63806712963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44851</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>45266</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>45317</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45309</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45471</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45011</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45380</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44946</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45244</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45121</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45477</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44979</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44812</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45266</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>44462</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>44918</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>45679</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44943</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44342</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45407</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45678</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45841.69503472222</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45666</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45671</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45089</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45415</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45722</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>44729</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45204</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45401</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45303</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45624</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45301</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45301</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45301</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45688</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>44494</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45301</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44210</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44467</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44133</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44064</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>44467</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>44195</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44904</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44641</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44230</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44848</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44935</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44437</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45371</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44498</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44175</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45336</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45103</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45475</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45253</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45121</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>44848</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44343</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45782</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45678</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45611</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44994</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45201</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44734</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45407.63753472222</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44825</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45799.44362268518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>45089</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45803.34567129629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44631</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45688</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45194</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45700</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>44314</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44342</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44336</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45813</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45302</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45604</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>44368</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>44867</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44361</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44697</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44935</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45232</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44054</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44054</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44092</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44138</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44294</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>44334</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>44278</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44309</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>44054</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>44158</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>44426</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44244</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44278</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44426</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>44820</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44393</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44650</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44512</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>44484</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>44054</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>44054</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>44082.63233796296</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44239</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44330</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44449</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44755</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44218</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44610</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44683</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44488</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44399</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44433</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44426</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44433</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44449</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44433</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44246</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44426</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44383</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>44546</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>44054</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44409</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44089</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>44286</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44176</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44334</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44064</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44335</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>44785</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>44140</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>44504</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44375</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>44369</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44302</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44887</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>44221</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44586</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44204</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44203</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>44111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>44588</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>44175</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44564</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44383</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44447</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>44298</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>44511</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44339</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>44369</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>44330</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44447</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>44447</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44867</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44141</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>44211</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>44312</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>44096</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44307</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>44795</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44204</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44179</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44433</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44162</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44398</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44158</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>44565</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>44461</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>44258</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44433</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44433</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44099</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44272</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44132</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44071</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44312</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44163</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44154</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44433</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44796</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44487</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44175</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>44571</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44187</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>44054</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44382</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>44237</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>44846</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44812</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44138</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44173</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>44756</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45743.33715277778</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45201</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45187</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45190</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45730</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44484</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>44851</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>44908</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45194</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45194</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45327</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>44923</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45075</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45068</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45424.98380787037</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>44942</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>44314</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45331</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>44785</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>44218</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>44641</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44977</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45362</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45068</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>44335</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45253</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>44930</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45643</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45331</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44848</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45012</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>44375</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44847</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45455</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44971</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45035</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45460</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44370</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45076</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>44848</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>44979</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>44979</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>44512</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45313</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>44112</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44783</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>45152</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45379</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45140</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>44393</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45302</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>45420</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45414</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45089</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45191</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45747.48170138889</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>44960</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45117</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45086</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45003</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45089</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>44651</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45454</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>44979</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45468</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44931</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>44977</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44785</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45371</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>44888</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45258</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45474</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45471</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>45016</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>45196</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45161</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45159</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45390</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45538</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>44944</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>44901</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44463</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45483</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>44474</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45244</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45747.48377314815</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>44956</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>44466</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>44937</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>44845</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45423,7 +45423,7 @@
         <v>45201</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45198</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45301</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>44938</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45093</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44091</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>44944</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44589</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45686</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>45460</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47126,7 +47126,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45306</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44912</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44912</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45538</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45035</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44977</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45476</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45272</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>44910</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>44621</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>45511</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44595</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45747.49021990741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49295,7 +49295,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45338</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49952,7 +49952,7 @@
         <v>45335</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45586.46196759259</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>44447</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45531</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45537</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45216</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>45321</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>44169</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45548.68</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45566</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45068</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52099,7 +52099,7 @@
         <v>44904</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52156,7 +52156,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45478</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>44646</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>44970</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>44615</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>45371</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>44748</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>45407.61327546297</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45077</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45797.34990740741</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -54035,7 +54035,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54221,7 +54221,7 @@
         <v>45049</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54278,7 +54278,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54392,7 +54392,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54677,7 +54677,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45093</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>45093</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45093</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45085</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>44669</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>44236</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55428,7 +55428,7 @@
         <v>44125</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55490,7 +55490,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45561</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55723,7 +55723,7 @@
         <v>45121</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55837,7 +55837,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55899,7 +55899,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55956,7 +55956,7 @@
         <v>45460</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>44783</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>44956</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -56189,7 +56189,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>45287</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45147</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56484,7 +56484,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56541,7 +56541,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56712,7 +56712,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56769,7 +56769,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>44939</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56883,7 +56883,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56940,7 +56940,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>44573</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -57178,7 +57178,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57235,7 +57235,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57297,7 +57297,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45245</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45265</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57706,7 +57706,7 @@
         <v>45148</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>44623</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45848.3125462963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45239</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45722</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45275</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45147</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45245</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>44964</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45153</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>44433</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>44180</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>44956</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45847</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -59104,7 +59104,7 @@
         <v>45847</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45847</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>45390.8940625</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59280,7 +59280,7 @@
         <v>45251</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59399,7 +59399,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59456,7 +59456,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59513,7 +59513,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>44977</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59823,7 +59823,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>44798</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>44342</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59994,7 +59994,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>44269</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -60108,7 +60108,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -60222,7 +60222,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60279,7 +60279,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60336,7 +60336,7 @@
         <v>45173</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60569,7 +60569,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60683,7 +60683,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60859,7 +60859,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         <v>45216</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60973,7 +60973,7 @@
         <v>45110</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         <v>45261</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -61216,7 +61216,7 @@
         <v>44064</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61335,7 +61335,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61454,7 +61454,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45272</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61744,7 +61744,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61801,7 +61801,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61858,7 +61858,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61915,7 +61915,7 @@
         <v>44984</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -62034,7 +62034,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45817</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -62148,7 +62148,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>45817.58832175926</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45477</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62386,7 +62386,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62443,7 +62443,7 @@
         <v>45140</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62500,7 +62500,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62557,7 +62557,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62614,7 +62614,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62671,7 +62671,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62728,7 +62728,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62785,7 +62785,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62842,7 +62842,7 @@
         <v>45734.68493055556</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45366</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62961,7 +62961,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -63023,7 +63023,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -63147,7 +63147,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -63204,7 +63204,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63328,7 +63328,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63385,7 +63385,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63442,7 +63442,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63499,7 +63499,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63618,7 +63618,7 @@
         <v>45040</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63675,7 +63675,7 @@
         <v>45510</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63732,7 +63732,7 @@
         <v>44655</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63789,7 +63789,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>45825.57315972223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -64017,7 +64017,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -64074,7 +64074,7 @@
         <v>44830</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -64131,7 +64131,7 @@
         <v>45678</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -64188,7 +64188,7 @@
         <v>45730</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64245,7 +64245,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64302,7 +64302,7 @@
         <v>45483</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64359,7 +64359,7 @@
         <v>45831</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64416,7 +64416,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64473,7 +64473,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>45301</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64587,7 +64587,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>44187</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64701,7 +64701,7 @@
         <v>45114</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64758,7 +64758,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64815,7 +64815,7 @@
         <v>45278</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64872,7 +64872,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64929,7 +64929,7 @@
         <v>45301</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64986,7 +64986,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -65043,7 +65043,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -65100,7 +65100,7 @@
         <v>45831</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -65157,7 +65157,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65214,7 +65214,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65271,7 +65271,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65328,7 +65328,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65390,7 +65390,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65452,7 +65452,7 @@
         <v>44935</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65571,7 +65571,7 @@
         <v>44368</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>45832.89177083333</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65685,7 +65685,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65747,7 +65747,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65809,7 +65809,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65866,7 +65866,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65928,7 +65928,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65990,7 +65990,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -66047,7 +66047,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -66104,7 +66104,7 @@
         <v>44908</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -66166,7 +66166,7 @@
         <v>45033</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66223,7 +66223,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66280,7 +66280,7 @@
         <v>45477</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66337,7 +66337,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66399,7 +66399,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45754.68405092593</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66570,7 +66570,7 @@
         <v>44152</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66684,7 +66684,7 @@
         <v>45338</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66746,7 +66746,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66803,7 +66803,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66860,7 +66860,7 @@
         <v>44904</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66917,7 +66917,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66974,7 +66974,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -67031,7 +67031,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -67088,7 +67088,7 @@
         <v>44646</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -67145,7 +67145,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67202,7 +67202,7 @@
         <v>44480</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>44176</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67373,7 +67373,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67430,7 +67430,7 @@
         <v>45079</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67487,7 +67487,7 @@
         <v>45140</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67544,7 +67544,7 @@
         <v>44987</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67601,7 +67601,7 @@
         <v>44623</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67663,7 +67663,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67725,7 +67725,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67787,7 +67787,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67844,7 +67844,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67906,7 +67906,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67963,7 +67963,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -68020,7 +68020,7 @@
         <v>44230</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -68077,7 +68077,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -68134,7 +68134,7 @@
         <v>44848</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68196,7 +68196,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68253,7 +68253,7 @@
         <v>44896</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68310,7 +68310,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68372,7 +68372,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>45040</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68491,7 +68491,7 @@
         <v>45104</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68548,7 +68548,7 @@
         <v>45730</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68605,7 +68605,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68662,7 +68662,7 @@
         <v>45021</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68719,7 +68719,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68781,7 +68781,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68838,7 +68838,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68895,7 +68895,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68952,7 +68952,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -69014,7 +69014,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -69190,7 +69190,7 @@
         <v>44924</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45030</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -69304,7 +69304,7 @@
         <v>44256</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69361,7 +69361,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -69423,7 +69423,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69485,7 +69485,7 @@
         <v>45540</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69547,7 +69547,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69604,7 +69604,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69718,7 +69718,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69775,7 +69775,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69832,7 +69832,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69889,7 +69889,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69946,7 +69946,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -70008,7 +70008,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -70070,7 +70070,7 @@
         <v>45483</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -70127,7 +70127,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -70189,7 +70189,7 @@
         <v>45036</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -70246,7 +70246,7 @@
         <v>45104</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45303</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44239</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>44393</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45434</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45525</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45244</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>44474</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44284</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>45473</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45671</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45585</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45468</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45551</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44505</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45604</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45686</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44795</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45638</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45502</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>44539</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44497</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>45237</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45551</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45686</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45677</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45473</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>44994</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45608</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45691</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44935</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44120</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45204</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45335</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45473</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45505</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>45671</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45475</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45502</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45841.69503472222</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45475</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44931</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44868</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45730</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>45425</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45363</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45722</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45232</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45435</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45811</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45834</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45274</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45301</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44896</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45699</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45635</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>45253</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44342</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44398</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45761</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45463</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44249</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44887</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45686</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45471</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45604</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>45671</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>45671</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>45611</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45314</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45548</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45737</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>45834</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45411</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44064</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45000</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45673</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44931</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45180</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45380</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45321</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44848</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45121</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45266</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44462</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45679</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45678</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44342</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45671</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45407</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45415</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44851</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45266</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45317</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45309</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45722</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45471</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45666</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44946</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45477</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44979</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45401</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45303</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>44918</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44729</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45204</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45624</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45301</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45301</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45301</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44943</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44494</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45688</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45301</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45089</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>44210</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44467</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44133</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45135</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45238</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45743.63806712963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45011</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45244</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>44064</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44467</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>44195</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45336</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45253</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44848</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45121</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45782</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45678</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44994</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45799.44362268518</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45803.34567129629</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44825</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45688</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45700</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>44175</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45475</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>44848</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45194</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45813</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44343</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44314</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45604</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45611</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45302</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44368</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45201</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45371</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44734</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>44867</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45089</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44631</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44361</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44697</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44935</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44342</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44336</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45232</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44904</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44641</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44230</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44935</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45371</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>44498</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44437</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45103</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44092</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44138</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44294</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>44334</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44278</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44309</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>44158</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44426</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44244</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44278</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44426</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44820</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>44393</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44650</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44512</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>44484</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44082.63233796296</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44239</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44330</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44449</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44755</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44218</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44610</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>44683</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44488</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44399</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44433</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44426</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44449</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>44433</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>44433</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44246</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44426</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>44383</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>44546</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>44409</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>44286</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44089</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44064</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44335</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44176</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44334</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44785</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44140</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44504</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>44375</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44369</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>44302</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44221</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>44887</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>44586</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>44204</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44203</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>44111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44588</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>44564</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44383</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>44447</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>44298</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>44511</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>44339</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44447</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44096</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44312</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44141</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>44211</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44307</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44795</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44179</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44204</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>44398</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44162</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>44433</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44158</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44565</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44461</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44433</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44258</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44433</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44099</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44272</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44132</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44071</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44796</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44163</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44433</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44487</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44154</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44175</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44571</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44187</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>44237</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44382</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44812</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44138</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>44173</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>44846</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44369</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44330</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44867</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45187</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45190</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44930</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45196</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45730</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45161</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45159</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45194</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45194</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45327</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45390</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45538</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45747.48377314815</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44847</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44944</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44370</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44848</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44901</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>44463</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>44512</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>44112</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>44956</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45379</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>45331</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45420</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45201</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45198</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45362</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>44938</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45093</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45686</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45306</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45035</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>44977</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45476</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44910</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>44621</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45338</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45335</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45586.46196759259</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45537</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45117</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45566</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45797.34990740741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45068</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45478</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45561</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>44646</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45287</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45086</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45371</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45407.61327546297</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45454</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45468</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45848.3125462963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45722</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45049</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45093</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45093</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45093</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>44669</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45258</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45847</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>44125</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45847</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45474</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45471</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45847</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45147</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45483</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>44474</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>44573</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45245</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>44466</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45148</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>44623</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>44937</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>44845</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>45239</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>45153</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>44091</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44180</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>44944</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>44589</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45460</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45251</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44912</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>44912</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45817</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45817.58832175926</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45538</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45173</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45272</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45216</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45110</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45825.57315972223</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45261</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>45511</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>44064</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>44595</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45272</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45831</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         <v>45747.49021990741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50169,7 +50169,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50226,7 +50226,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>44447</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50345,7 +50345,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45734.68493055556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>45366</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45531</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>45831</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51225,7 +51225,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45216</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>45832.89177083333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52053,7 +52053,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52172,7 +52172,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         <v>45321</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>45301</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>44169</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52467,7 +52467,7 @@
         <v>45114</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>45548.68</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52581,7 +52581,7 @@
         <v>45877</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>45877</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45877</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>45278</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>45877</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45301</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53218,7 +53218,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>44935</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53679,7 +53679,7 @@
         <v>44368</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53736,7 +53736,7 @@
         <v>45880</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>44904</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>44908</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>45033</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54544,7 +54544,7 @@
         <v>45883</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54658,7 +54658,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45477</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54891,7 +54891,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54948,7 +54948,7 @@
         <v>44970</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>44615</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55206,7 +55206,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55263,7 +55263,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55320,7 +55320,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55377,7 +55377,7 @@
         <v>44152</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>44748</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45338</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55729,7 +55729,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>45077</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>44904</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45085</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>44236</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>44646</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>44480</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45121</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44176</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56884,7 +56884,7 @@
         <v>45460</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>44783</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>44956</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45079</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45140</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>44987</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>44623</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57588,7 +57588,7 @@
         <v>44939</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57645,7 +57645,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57935,7 +57935,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58282,7 +58282,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58339,7 +58339,7 @@
         <v>45275</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58577,7 +58577,7 @@
         <v>44230</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>44964</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58691,7 +58691,7 @@
         <v>44433</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58748,7 +58748,7 @@
         <v>44956</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58805,7 +58805,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>45390.8940625</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>44848</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58986,7 +58986,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -59043,7 +59043,7 @@
         <v>44977</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -59162,7 +59162,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>44798</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59276,7 +59276,7 @@
         <v>44896</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59395,7 +59395,7 @@
         <v>44342</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59452,7 +59452,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>44269</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45104</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>45730</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59913,7 +59913,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>45021</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -60146,7 +60146,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60260,7 +60260,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60493,7 +60493,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60550,7 +60550,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60669,7 +60669,7 @@
         <v>44924</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60783,7 +60783,7 @@
         <v>44984</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60840,7 +60840,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60902,7 +60902,7 @@
         <v>45030</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60959,7 +60959,7 @@
         <v>44256</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -61016,7 +61016,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45477</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>45140</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61197,7 +61197,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61259,7 +61259,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61321,7 +61321,7 @@
         <v>45540</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45483</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -62025,7 +62025,7 @@
         <v>45036</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -62082,7 +62082,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>45104</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62263,7 +62263,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62325,7 +62325,7 @@
         <v>45510</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>44655</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62501,7 +62501,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62620,7 +62620,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62677,7 +62677,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>44830</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45678</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62967,7 +62967,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -63024,7 +63024,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -63086,7 +63086,7 @@
         <v>45730</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -63143,7 +63143,7 @@
         <v>44484</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63200,7 +63200,7 @@
         <v>44908</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63257,7 +63257,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>45483</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63371,7 +63371,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63433,7 +63433,7 @@
         <v>45068</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63490,7 +63490,7 @@
         <v>45424.98380787037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63552,7 +63552,7 @@
         <v>44942</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>44187</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63847,7 +63847,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63904,7 +63904,7 @@
         <v>44785</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63961,7 +63961,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -64018,7 +64018,7 @@
         <v>44641</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -64080,7 +64080,7 @@
         <v>45743.33715277778</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64194,7 +64194,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64251,7 +64251,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>44335</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64365,7 +64365,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64422,7 +64422,7 @@
         <v>44851</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64479,7 +64479,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64536,7 +64536,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64650,7 +64650,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>45643</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64769,7 +64769,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64826,7 +64826,7 @@
         <v>44923</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64883,7 +64883,7 @@
         <v>45012</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45075</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64997,7 +64997,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -65054,7 +65054,7 @@
         <v>44314</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -65116,7 +65116,7 @@
         <v>45455</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65178,7 +65178,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65235,7 +65235,7 @@
         <v>45460</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65292,7 +65292,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65354,7 +65354,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65411,7 +65411,7 @@
         <v>44979</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65468,7 +65468,7 @@
         <v>44979</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65525,7 +65525,7 @@
         <v>44218</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65582,7 +65582,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65639,7 +65639,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65696,7 +65696,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65758,7 +65758,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65820,7 +65820,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65882,7 +65882,7 @@
         <v>44977</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>44783</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45068</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -66110,7 +66110,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66172,7 +66172,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66229,7 +66229,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66286,7 +66286,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>44848</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45414</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>44375</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66762,7 +66762,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66824,7 +66824,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66886,7 +66886,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66943,7 +66943,7 @@
         <v>44971</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -67000,7 +67000,7 @@
         <v>45035</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -67057,7 +67057,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -67114,7 +67114,7 @@
         <v>45076</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67228,7 +67228,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67285,7 +67285,7 @@
         <v>45747.48170138889</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
         <v>44960</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67399,7 +67399,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67461,7 +67461,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67518,7 +67518,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67575,7 +67575,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67632,7 +67632,7 @@
         <v>45152</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67709,7 +67709,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67766,7 +67766,7 @@
         <v>45140</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67823,7 +67823,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45003</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67957,7 +67957,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -68014,7 +68014,7 @@
         <v>44393</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -68071,7 +68071,7 @@
         <v>44979</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -68128,7 +68128,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68242,7 +68242,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68299,7 +68299,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68356,7 +68356,7 @@
         <v>44931</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68418,7 +68418,7 @@
         <v>44977</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>44785</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68532,7 +68532,7 @@
         <v>45089</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68589,7 +68589,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68646,7 +68646,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68703,7 +68703,7 @@
         <v>45191</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68765,7 +68765,7 @@
         <v>45371</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68822,7 +68822,7 @@
         <v>44888</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68879,7 +68879,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -69003,7 +69003,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -69060,7 +69060,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -69122,7 +69122,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -69179,7 +69179,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -69236,7 +69236,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -69298,7 +69298,7 @@
         <v>45089</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69355,7 +69355,7 @@
         <v>44651</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -69412,7 +69412,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69593,7 +69593,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69650,7 +69650,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69764,7 +69764,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69821,7 +69821,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69878,7 +69878,7 @@
         <v>45016</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69935,7 +69935,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69997,7 +69997,7 @@
         <v>45244</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45303</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44239</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>44393</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45434</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45525</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45244</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>44474</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44284</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>45473</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45671</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45585</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45468</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45551</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44505</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45604</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45686</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44795</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45638</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45502</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>44539</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44497</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>45237</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45551</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45686</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45677</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45473</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>44994</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45608</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45691</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44935</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44120</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45204</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45335</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45473</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45505</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>45671</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45475</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45502</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45841.69503472222</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45475</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44931</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44868</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45730</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>45425</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45363</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45722</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45232</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45435</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45811</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45834</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45274</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45301</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44896</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45699</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45635</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>45253</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44342</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44398</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45761</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45463</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44249</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44887</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45686</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45471</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45604</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>45671</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>45671</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>45611</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45314</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45548</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45737</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>45834</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45411</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44064</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45000</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45673</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44931</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45180</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45380</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45321</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44848</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>44812</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45121</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45266</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44462</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45679</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45678</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44342</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45671</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45407</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45415</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44851</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45266</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45317</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45309</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45722</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45471</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45666</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44946</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45477</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44979</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45401</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45303</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>44918</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44729</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45204</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45624</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45301</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45301</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45301</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44943</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44494</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45688</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45301</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45089</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>44210</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44467</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>44133</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45135</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45238</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45743.63806712963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45011</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45244</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>44064</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44467</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>44195</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45336</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45253</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44848</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45121</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45782</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45678</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44994</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45799.44362268518</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45803.34567129629</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44825</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45688</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45700</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>44175</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45475</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>44848</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45194</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45813</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44343</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44314</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45604</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45611</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45302</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44368</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45201</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45371</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44734</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>44867</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45089</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44631</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44361</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44697</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44935</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44342</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>44336</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45232</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44904</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44641</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44230</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44935</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45371</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>44498</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44437</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45103</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44092</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44138</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44294</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>44334</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44278</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44309</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>44158</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44426</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44244</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44278</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44426</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44820</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>44393</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44650</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44512</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>44484</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44082.63233796296</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44239</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44330</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44449</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44755</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44218</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44610</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>44683</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44488</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44399</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>44433</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44426</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44449</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>44433</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>44433</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44246</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44426</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>44383</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>44546</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>44409</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>44286</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44089</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44064</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44335</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44176</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44334</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44785</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44140</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44504</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>44375</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44369</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>44302</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44221</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>44887</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>44586</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>44204</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44203</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>44111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44588</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>44564</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44383</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>44447</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>44298</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>44511</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>44339</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44447</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44096</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44312</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44141</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>44211</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44307</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44795</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44179</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44204</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>44398</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44162</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>44433</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44158</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44565</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44461</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44433</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44258</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44433</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44099</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>44272</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>44132</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>44071</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44796</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44163</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44433</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44487</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44154</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44175</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44571</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44187</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>44237</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44382</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44812</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44138</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>44173</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>44846</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44369</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44330</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>44867</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45187</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45190</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44930</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45196</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45730</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45161</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45159</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45194</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45194</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45327</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45390</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45538</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45747.48377314815</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44847</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44944</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44370</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44848</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44901</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>44463</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>44512</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>44112</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>44956</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45379</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>45331</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45420</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45201</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45198</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45362</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>44938</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45093</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45686</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45306</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45035</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>44977</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45476</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44910</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>44621</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45338</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45335</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45586.46196759259</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45537</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45117</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45566</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45797.34990740741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45068</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45478</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45561</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>44646</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45287</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45086</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45371</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45407.61327546297</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45454</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45468</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45848.3125462963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45722</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45049</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45093</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45093</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45093</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>44669</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45258</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45847</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>44125</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45847</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45474</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45471</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45847</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45147</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45483</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>44474</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>44573</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45245</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>44466</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45148</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>44623</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>44937</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>44845</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>45239</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>45153</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>44091</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44180</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>44944</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>44589</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45460</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45251</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44912</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>44912</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45817</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45817.58832175926</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45538</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45173</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45272</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45216</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45110</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45825.57315972223</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45261</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>45511</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>44064</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>44595</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45272</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45831</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         <v>45747.49021990741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50169,7 +50169,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50226,7 +50226,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>44447</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50345,7 +50345,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45734.68493055556</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>45366</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45531</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>45831</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51225,7 +51225,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45216</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>45832.89177083333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52053,7 +52053,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52172,7 +52172,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         <v>45321</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>45301</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>44169</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52467,7 +52467,7 @@
         <v>45114</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>45548.68</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52581,7 +52581,7 @@
         <v>45877</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>45877</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45877</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>45278</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52866,7 +52866,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>45877</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45301</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53218,7 +53218,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>44935</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53679,7 +53679,7 @@
         <v>44368</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53736,7 +53736,7 @@
         <v>45880</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>44904</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>44908</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>45033</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54544,7 +54544,7 @@
         <v>45883</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54658,7 +54658,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45477</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54891,7 +54891,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54948,7 +54948,7 @@
         <v>44970</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>44615</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55206,7 +55206,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55263,7 +55263,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55320,7 +55320,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55377,7 +55377,7 @@
         <v>44152</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>44748</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45338</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55729,7 +55729,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>45077</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>44904</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45085</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>44236</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>44646</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>44480</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45121</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44176</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56884,7 +56884,7 @@
         <v>45460</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>44783</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>44956</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45079</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45140</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>44987</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>44623</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57588,7 +57588,7 @@
         <v>44939</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57645,7 +57645,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45265</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57935,7 +57935,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58282,7 +58282,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58339,7 +58339,7 @@
         <v>45275</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>45245</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58577,7 +58577,7 @@
         <v>44230</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>44964</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58691,7 +58691,7 @@
         <v>44433</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58748,7 +58748,7 @@
         <v>44956</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58805,7 +58805,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>45390.8940625</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>44848</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58986,7 +58986,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -59043,7 +59043,7 @@
         <v>44977</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -59162,7 +59162,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>44798</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59276,7 +59276,7 @@
         <v>44896</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59395,7 +59395,7 @@
         <v>44342</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59452,7 +59452,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>44269</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45104</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>45730</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59913,7 +59913,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>45021</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -60146,7 +60146,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60260,7 +60260,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60493,7 +60493,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60550,7 +60550,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60669,7 +60669,7 @@
         <v>44924</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60783,7 +60783,7 @@
         <v>44984</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60840,7 +60840,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60902,7 +60902,7 @@
         <v>45030</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60959,7 +60959,7 @@
         <v>44256</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -61016,7 +61016,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45477</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>45140</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61197,7 +61197,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61259,7 +61259,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61321,7 +61321,7 @@
         <v>45540</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45483</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -62025,7 +62025,7 @@
         <v>45036</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -62082,7 +62082,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>45104</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62263,7 +62263,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62325,7 +62325,7 @@
         <v>45510</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>44655</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62501,7 +62501,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62620,7 +62620,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62677,7 +62677,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>44830</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62848,7 +62848,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>45678</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62967,7 +62967,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -63024,7 +63024,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -63086,7 +63086,7 @@
         <v>45730</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -63143,7 +63143,7 @@
         <v>44484</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63200,7 +63200,7 @@
         <v>44908</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63257,7 +63257,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>45483</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63371,7 +63371,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63433,7 +63433,7 @@
         <v>45068</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63490,7 +63490,7 @@
         <v>45424.98380787037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63552,7 +63552,7 @@
         <v>44942</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>44187</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63847,7 +63847,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63904,7 +63904,7 @@
         <v>44785</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63961,7 +63961,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -64018,7 +64018,7 @@
         <v>44641</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -64080,7 +64080,7 @@
         <v>45743.33715277778</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45201</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64194,7 +64194,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64251,7 +64251,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>44335</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64365,7 +64365,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64422,7 +64422,7 @@
         <v>44851</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64479,7 +64479,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64536,7 +64536,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64650,7 +64650,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>45643</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64769,7 +64769,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64826,7 +64826,7 @@
         <v>44923</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64883,7 +64883,7 @@
         <v>45012</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45075</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64997,7 +64997,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -65054,7 +65054,7 @@
         <v>44314</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -65116,7 +65116,7 @@
         <v>45455</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65178,7 +65178,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65235,7 +65235,7 @@
         <v>45460</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65292,7 +65292,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65354,7 +65354,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65411,7 +65411,7 @@
         <v>44979</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65468,7 +65468,7 @@
         <v>44979</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65525,7 +65525,7 @@
         <v>44218</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65582,7 +65582,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65639,7 +65639,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65696,7 +65696,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65758,7 +65758,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65820,7 +65820,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65882,7 +65882,7 @@
         <v>44977</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>44783</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45068</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -66110,7 +66110,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66172,7 +66172,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66229,7 +66229,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66286,7 +66286,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>44848</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45414</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>44375</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66762,7 +66762,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66824,7 +66824,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66886,7 +66886,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66943,7 +66943,7 @@
         <v>44971</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -67000,7 +67000,7 @@
         <v>45035</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -67057,7 +67057,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -67114,7 +67114,7 @@
         <v>45076</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67228,7 +67228,7 @@
         <v>45313</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67285,7 +67285,7 @@
         <v>45747.48170138889</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
         <v>44960</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67399,7 +67399,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67461,7 +67461,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67518,7 +67518,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67575,7 +67575,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67632,7 +67632,7 @@
         <v>45152</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67709,7 +67709,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67766,7 +67766,7 @@
         <v>45140</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67823,7 +67823,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45003</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67957,7 +67957,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -68014,7 +68014,7 @@
         <v>44393</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -68071,7 +68071,7 @@
         <v>44979</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -68128,7 +68128,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68242,7 +68242,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68299,7 +68299,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68356,7 +68356,7 @@
         <v>44931</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68418,7 +68418,7 @@
         <v>44977</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>44785</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68532,7 +68532,7 @@
         <v>45089</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68589,7 +68589,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68646,7 +68646,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68703,7 +68703,7 @@
         <v>45191</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68765,7 +68765,7 @@
         <v>45371</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68822,7 +68822,7 @@
         <v>44888</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68879,7 +68879,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68941,7 +68941,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -69003,7 +69003,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -69060,7 +69060,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -69122,7 +69122,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -69179,7 +69179,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -69236,7 +69236,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -69298,7 +69298,7 @@
         <v>45089</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69355,7 +69355,7 @@
         <v>44651</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -69412,7 +69412,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69593,7 +69593,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -69650,7 +69650,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -69707,7 +69707,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -69764,7 +69764,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -69821,7 +69821,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -69878,7 +69878,7 @@
         <v>45016</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -69935,7 +69935,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -69997,7 +69997,7 @@
         <v>45244</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45303</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44393</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>44239</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45525</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45530</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>44284</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44474</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45244</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45434</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>45468</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45671</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45473</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45551</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>45638</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44505</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45790</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45604</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>45686</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45502</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44539</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44497</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>44120</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44994</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45551</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45204</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45686</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45677</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>45237</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45473</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44935</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45608</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45691</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45730</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45505</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45475</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45671</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44868</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44931</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45841.69503472222</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>45502</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45475</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45473</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45761</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44398</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44342</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45635</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45274</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>45722</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45811</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45435</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45834</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45363</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>45232</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45301</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>45463</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45699</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44896</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45253</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44249</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45611</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>45180</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45314</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44931</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44887</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>45686</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45548</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45673</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45411</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45000</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45604</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45671</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45671</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45471</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45737</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45834</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45624</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45380</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45011</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45238</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44812</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45089</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45301</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45301</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45407</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44494</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45266</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45309</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45679</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45471</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44979</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>45678</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>44342</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45722</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45671</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45317</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45415</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44462</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44848</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>45266</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45303</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45401</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45204</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45666</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44918</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44210</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45301</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44729</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44133</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44943</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45121</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44851</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45135</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45244</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45477</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44946</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45688</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44467</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45743.63806712963</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45301</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45321</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44467</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44195</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44935</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45232</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44825</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>44867</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45103</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44641</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44848</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>44734</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45089</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44175</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45121</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45611</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44904</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>44336</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44361</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45678</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45782</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>45336</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>44697</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>44498</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>44994</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45475</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>44437</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45803.34567129629</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>44314</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45700</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44342</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44343</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45813</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>45194</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45604</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45302</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44935</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44230</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45371</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44631</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45201</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45688</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45371</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44848</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44368</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45253</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>44092</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>44138</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>44294</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>44334</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>44278</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44309</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>44158</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44426</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>44244</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44278</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44820</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44426</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44393</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44650</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44512</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44484</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44082.63233796296</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44239</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44330</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>44449</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44755</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44218</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44610</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>44683</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44488</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>44399</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44433</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44426</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>44449</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>44433</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>44433</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44246</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44426</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44383</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44546</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44409</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>44286</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44335</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44176</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44334</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>44089</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>44140</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>44785</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>44504</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>44375</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44369</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>44302</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>44221</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44887</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44586</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>44204</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>44203</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>44111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44111</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44588</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44175</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44564</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44383</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>44447</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44298</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44511</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>44339</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>44369</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>44330</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44867</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>44447</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44141</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44211</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44447</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44307</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>44312</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>44096</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>44795</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>44204</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44433</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>44179</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>44398</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44162</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>44158</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44565</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44272</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>44099</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>44461</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44132</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>44433</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44433</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44071</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44312</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44796</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44175</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44163</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>44154</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44571</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44187</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44433</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44487</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44382</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>44846</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44756</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45302</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45460</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45538</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>44237</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>44370</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45147</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>44812</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44138</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45049</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44979</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45531</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44595</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>44904</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44342</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>45730</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>45251</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45161</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45414</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45313</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45016</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45012</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35368,7 +35368,7 @@
         <v>45021</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44463</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>44589</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>44851</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45033</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45278</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44783</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44956</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44888</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45747.48377314815</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>44641</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45187</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44848</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45327</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44748</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44512</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45483</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45730</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44964</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45173</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45153</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45079</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45338</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>44176</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>45379</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45191</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45077</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45306</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>44935</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>44218</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45093</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45093</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45093</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45537</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>44956</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45068</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45114</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44623</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>44314</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>44830</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45478</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>45140</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44433</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45371</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>44783</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
         <v>45538</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>44169</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>45407.61327546297</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>44901</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45455</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45424.98380787037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45265</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45194</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45194</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>44474</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>45140</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43516,7 +43516,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>44480</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45244</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45686</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>44970</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>45548.68</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>44939</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45511</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>44910</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45476</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>44930</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>45734.68493055556</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45362</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45190</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>45338</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>44621</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>44466</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45272</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45678</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45198</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45390</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45148</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45245</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47143,7 +47143,7 @@
         <v>45474</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45797.34990740741</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45086</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>44977</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45335</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45275</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45261</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45483</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45121</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45460</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45460</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>44112</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45747.49021990741</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>44942</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>45561</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>45477</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44447</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45152</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45287</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45239</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45245</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>44845</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50574,7 +50574,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45722</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45366</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51459,7 +51459,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51573,7 +51573,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>44912</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51863,7 +51863,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -51987,7 +51987,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>44180</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52225,7 +52225,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>45468</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45003</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45036</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52768,7 +52768,7 @@
         <v>44977</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52882,7 +52882,7 @@
         <v>45390.8940625</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>44484</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45331</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45110</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>44375</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>44960</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45566</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>44785</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>44573</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54114,7 +54114,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54171,7 +54171,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45817</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54347,7 +54347,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>45817.58832175926</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54466,7 +54466,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>44125</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54585,7 +54585,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>44904</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54699,7 +54699,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54756,7 +54756,7 @@
         <v>44269</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54813,7 +54813,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54932,7 +54932,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54989,7 +54989,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>44896</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>45201</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55160,7 +55160,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45040</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>45420</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55559,7 +55559,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55616,7 +55616,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55673,7 +55673,7 @@
         <v>45483</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55730,7 +55730,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55787,7 +55787,7 @@
         <v>45068</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>44615</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56077,7 +56077,7 @@
         <v>44944</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45301</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56647,7 +56647,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45085</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45035</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45825.57315972223</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45104</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45089</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>44256</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>44091</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>45159</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57693,7 +57693,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57807,7 +57807,7 @@
         <v>45540</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45331</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>44908</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58107,7 +58107,7 @@
         <v>45831</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>45831</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58278,7 +58278,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>45471</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>45147</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>44944</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45117</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>44938</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59644,7 +59644,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45877</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45877</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -60001,7 +60001,7 @@
         <v>45477</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -60058,7 +60058,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>44908</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60239,7 +60239,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60415,7 +60415,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60596,7 +60596,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60658,7 +60658,7 @@
         <v>44623</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60720,7 +60720,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60782,7 +60782,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45201</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45196</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61201,7 +61201,7 @@
         <v>45104</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>45877</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>45877</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61377,7 +61377,7 @@
         <v>44335</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61434,7 +61434,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61558,7 +61558,7 @@
         <v>44977</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61615,7 +61615,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61672,7 +61672,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61729,7 +61729,7 @@
         <v>44230</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61786,7 +61786,7 @@
         <v>44798</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61843,7 +61843,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61900,7 +61900,7 @@
         <v>44669</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         <v>45454</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62133,7 +62133,7 @@
         <v>44847</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62190,7 +62190,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62247,7 +62247,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62371,7 +62371,7 @@
         <v>44236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62428,7 +62428,7 @@
         <v>44984</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62485,7 +62485,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62542,7 +62542,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62599,7 +62599,7 @@
         <v>44924</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62713,7 +62713,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62770,7 +62770,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62827,7 +62827,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62941,7 +62941,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63127,7 +63127,7 @@
         <v>45040</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63189,7 +63189,7 @@
         <v>45093</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63303,7 +63303,7 @@
         <v>44923</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63360,7 +63360,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63422,7 +63422,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>44977</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63536,7 +63536,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63593,7 +63593,7 @@
         <v>45258</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63650,7 +63650,7 @@
         <v>44152</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>44646</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63764,7 +63764,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63821,7 +63821,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63935,7 +63935,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -64049,7 +64049,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64106,7 +64106,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64163,7 +64163,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64220,7 +64220,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64277,7 +64277,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64334,7 +64334,7 @@
         <v>44912</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64396,7 +64396,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64453,7 +64453,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64567,7 +64567,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64624,7 +64624,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64681,7 +64681,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64738,7 +64738,7 @@
         <v>45321</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64800,7 +64800,7 @@
         <v>45030</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64919,7 +64919,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64981,7 +64981,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -65043,7 +65043,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65105,7 +65105,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65167,7 +65167,7 @@
         <v>45301</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65281,7 +65281,7 @@
         <v>45089</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65338,7 +65338,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65395,7 +65395,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65452,7 +65452,7 @@
         <v>45216</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65566,7 +65566,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65643,7 +65643,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>45883</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65757,7 +65757,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65819,7 +65819,7 @@
         <v>45880</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65876,7 +65876,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65933,7 +65933,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -66057,7 +66057,7 @@
         <v>45847</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66114,7 +66114,7 @@
         <v>45847</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66171,7 +66171,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66228,7 +66228,7 @@
         <v>45889.67606481481</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66285,7 +66285,7 @@
         <v>45889.67436342593</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66342,7 +66342,7 @@
         <v>45889.6947337963</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66399,7 +66399,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>44655</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45889.67297453704</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66570,7 +66570,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66632,7 +66632,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66689,7 +66689,7 @@
         <v>44393</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66746,7 +66746,7 @@
         <v>45068</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66803,7 +66803,7 @@
         <v>45730</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66860,7 +66860,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66917,7 +66917,7 @@
         <v>45847</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66974,7 +66974,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -67031,7 +67031,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67088,7 +67088,7 @@
         <v>45848</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67145,7 +67145,7 @@
         <v>45076</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67202,7 +67202,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67378,7 +67378,7 @@
         <v>45371</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67435,7 +67435,7 @@
         <v>44987</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67492,7 +67492,7 @@
         <v>44848</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67554,7 +67554,7 @@
         <v>44187</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67611,7 +67611,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67668,7 +67668,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67725,7 +67725,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67782,7 +67782,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67839,7 +67839,7 @@
         <v>44368</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67896,7 +67896,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67953,7 +67953,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -68010,7 +68010,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68067,7 +68067,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68124,7 +68124,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68181,7 +68181,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68238,7 +68238,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68357,7 +68357,7 @@
         <v>44979</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68414,7 +68414,7 @@
         <v>44979</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68471,7 +68471,7 @@
         <v>45035</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68528,7 +68528,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68585,7 +68585,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68642,7 +68642,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68704,7 +68704,7 @@
         <v>45301</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68761,7 +68761,7 @@
         <v>45140</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68818,7 +68818,7 @@
         <v>44971</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68875,7 +68875,7 @@
         <v>44651</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68932,7 +68932,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68994,7 +68994,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -69051,7 +69051,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -69113,7 +69113,7 @@
         <v>44785</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -69170,7 +69170,7 @@
         <v>45253</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69227,7 +69227,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>44646</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -69341,7 +69341,7 @@
         <v>45643</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
         <v>44848</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -69460,7 +69460,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45303</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44239</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>44393</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45434</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45244</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45525</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44474</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45530</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44284</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>45671</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45468</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45551</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>44505</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>45790</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45686</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44795</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45638</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45604</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45502</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44539</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44497</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45237</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45551</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45473</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45686</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44994</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45677</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>44935</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45691</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45608</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45204</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45335</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44120</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45473</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>45505</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45475</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45671</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44931</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45841.69503472222</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45502</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>45475</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44868</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45730</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45425</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45363</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45722</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45435</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45811</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>45232</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>45274</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45635</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44896</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45699</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44342</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>45301</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44398</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>45834</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45253</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45463</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44249</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44887</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45686</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45471</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45671</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45671</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>45611</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45548</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45411</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45314</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45000</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45737</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45834</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45604</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>44931</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45180</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45673</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45380</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45321</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44848</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44812</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45266</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>45121</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44462</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45679</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>44851</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45266</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45317</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45309</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45471</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44946</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45477</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44979</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45678</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44918</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45671</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45415</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45722</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44342</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45407</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45303</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45666</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44943</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44729</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45204</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45089</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45624</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45688</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45301</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45301</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45301</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44467</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45401</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44494</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45238</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45301</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44210</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44133</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45011</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45135</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45244</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44467</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44195</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45336</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45253</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44848</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45121</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45782</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45678</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>44175</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>44994</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44848</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>44343</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45803.34567129629</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45700</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44825</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45611</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45813</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45201</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45604</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>44734</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45194</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44314</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45089</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>44631</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45371</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45302</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45688</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45371</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44342</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44336</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>44368</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44867</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44361</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>44697</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44935</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44437</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45232</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>44904</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44641</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44230</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44935</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44498</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45103</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44138</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44294</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44334</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44278</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44309</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>44158</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44426</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>44244</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44278</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44426</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>44820</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44393</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44650</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>44512</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44484</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44082.63233796296</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44239</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44330</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44449</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44755</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44218</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44610</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44683</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44488</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44399</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44433</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44426</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44449</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44433</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44433</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>44246</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>44426</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44383</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44546</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44409</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44286</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44176</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>44089</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44335</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44334</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44140</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44785</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44504</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44375</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44302</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44887</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44221</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44586</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44204</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>44203</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>44111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>44111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44588</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44175</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>44564</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44383</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44298</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44447</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44511</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>44339</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>44447</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>44369</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>44447</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44330</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>44096</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44867</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44141</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44211</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44312</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44795</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44307</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44179</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44204</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44398</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44433</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44158</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44565</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>44461</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>44433</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>44433</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>44272</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44099</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>44796</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44312</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>44132</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44433</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44487</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44175</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44163</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44154</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>44571</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>44187</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44237</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>44812</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44138</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44173</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>44846</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45331</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45196</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45161</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45362</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45187</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45190</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45159</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45730</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44930</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45194</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45194</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45327</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45390</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45538</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44944</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44901</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>44463</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44847</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>44370</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>44848</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45301</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44512</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44112</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44956</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45379</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45201</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45198</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>44938</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45420</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>45093</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45686</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45117</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45086</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45454</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45468</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45306</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45258</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45035</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44977</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45474</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45338</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45471</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>44910</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45335</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45483</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>44474</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>45537</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44466</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>44937</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44845</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45797.34990740741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>44091</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44944</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45566</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>44589</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45561</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45287</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45068</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>45460</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>44912</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>44912</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45478</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45538</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45722</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>44646</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45272</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45371</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45407.61327546297</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43866,7 +43866,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45511</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44595</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45049</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45093</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45093</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45093</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>44669</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44125</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44447</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45531</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45216</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45321</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>44169</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45548.68</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45147</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>44573</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45245</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45831</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44623</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>44615</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45239</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>44748</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45147</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45831</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45153</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>44180</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45077</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45251</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45085</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>44236</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45121</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45173</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50267,7 +50267,7 @@
         <v>45460</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45877</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45877</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45877</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>44783</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45877</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45216</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>44939</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45110</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45261</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45880</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>45272</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45265</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52691,7 +52691,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
         <v>45275</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45734.68493055556</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45245</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45366</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53514,7 +53514,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>44964</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>44433</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>44956</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45883</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45390.8940625</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45847</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>45847</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45848</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45889.67297453704</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54788,7 +54788,7 @@
         <v>45889.67606481481</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54902,7 +54902,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45847</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45889.6947337963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>44798</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45040</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45371</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45889.67436342593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>44342</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>44269</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45301</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45114</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45894.62219907407</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45894.62775462963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45278</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45894.39395833333</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>45301</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56617,7 +56617,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56731,7 +56731,7 @@
         <v>45898.62226851852</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>44935</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56902,7 +56902,7 @@
         <v>44368</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56959,7 +56959,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>44984</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>45898.80314814814</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45477</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45140</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>44908</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57549,7 +57549,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45477</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57839,7 +57839,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57896,7 +57896,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>44152</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>44655</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58129,7 +58129,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58243,7 +58243,7 @@
         <v>44830</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58357,7 +58357,7 @@
         <v>45678</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>45730</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58528,7 +58528,7 @@
         <v>45338</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>45483</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58647,7 +58647,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>44187</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58818,7 +58818,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58880,7 +58880,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>45201</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>44851</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>44904</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59279,7 +59279,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>44646</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59621,7 +59621,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>44923</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>44480</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>45075</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59849,7 +59849,7 @@
         <v>44176</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>44314</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60087,7 +60087,7 @@
         <v>44218</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60144,7 +60144,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>44977</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45079</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45140</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>44987</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>44623</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60791,7 +60791,7 @@
         <v>45068</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60967,7 +60967,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>45331</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61267,7 +61267,7 @@
         <v>44848</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>44375</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61505,7 +61505,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61567,7 +61567,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61686,7 +61686,7 @@
         <v>44971</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>45035</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61800,7 +61800,7 @@
         <v>45076</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45313</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61971,7 +61971,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>45152</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62162,7 +62162,7 @@
         <v>44230</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>45140</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>44393</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62447,7 +62447,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62504,7 +62504,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45089</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45191</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44848</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62804,7 +62804,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>44896</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>45089</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>44651</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63213,7 +63213,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63275,7 +63275,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>45040</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63399,7 +63399,7 @@
         <v>45104</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63456,7 +63456,7 @@
         <v>45730</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63513,7 +63513,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63627,7 +63627,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45016</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63741,7 +63741,7 @@
         <v>45021</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63798,7 +63798,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63860,7 +63860,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63917,7 +63917,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63974,7 +63974,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64031,7 +64031,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64093,7 +64093,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64150,7 +64150,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64269,7 +64269,7 @@
         <v>44924</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64326,7 +64326,7 @@
         <v>45030</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64383,7 +64383,7 @@
         <v>44256</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>45540</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64683,7 +64683,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64740,7 +64740,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64797,7 +64797,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64854,7 +64854,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65030,7 +65030,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45483</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65149,7 +65149,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65211,7 +65211,7 @@
         <v>45036</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>45104</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65392,7 +65392,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65454,7 +65454,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65692,7 +65692,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>44484</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>44908</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65987,7 +65987,7 @@
         <v>45068</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66044,7 +66044,7 @@
         <v>45424.98380787037</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         <v>44942</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66163,7 +66163,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66225,7 +66225,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66282,7 +66282,7 @@
         <v>44785</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>44641</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66401,7 +66401,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66458,7 +66458,7 @@
         <v>44335</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66515,7 +66515,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66572,7 +66572,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66629,7 +66629,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66691,7 +66691,7 @@
         <v>45643</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>45012</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66862,7 +66862,7 @@
         <v>45455</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66924,7 +66924,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>45460</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67095,7 +67095,7 @@
         <v>44979</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67152,7 +67152,7 @@
         <v>44979</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67209,7 +67209,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>44783</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67385,7 +67385,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67442,7 +67442,7 @@
         <v>45414</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67499,7 +67499,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67556,7 +67556,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67675,7 +67675,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67732,7 +67732,7 @@
         <v>44960</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67789,7 +67789,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67908,7 +67908,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67965,7 +67965,7 @@
         <v>45003</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68042,7 +68042,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68099,7 +68099,7 @@
         <v>44979</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68156,7 +68156,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68213,7 +68213,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68270,7 +68270,7 @@
         <v>44931</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68332,7 +68332,7 @@
         <v>44977</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68389,7 +68389,7 @@
         <v>44785</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68446,7 +68446,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68503,7 +68503,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68560,7 +68560,7 @@
         <v>44888</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68617,7 +68617,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68679,7 +68679,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68736,7 +68736,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68793,7 +68793,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68912,7 +68912,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68969,7 +68969,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -69026,7 +69026,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -69083,7 +69083,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69202,7 +69202,7 @@
         <v>45244</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45303</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44239</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>44393</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45434</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45244</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45525</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44474</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45530</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44284</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>45671</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>45473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45468</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45551</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>44505</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>45790</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45686</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>44795</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45638</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45604</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45502</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44539</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44497</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45237</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45551</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45473</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45686</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44994</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45677</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>44935</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45691</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45608</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>45204</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45335</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44120</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45473</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>45505</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45475</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45671</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44931</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45841.69503472222</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45502</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>45475</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44868</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45730</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45425</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45363</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45722</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45435</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45811</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>45232</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>45274</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45635</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>44896</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45699</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44342</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>45301</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44398</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>45834</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45253</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45463</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44249</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44887</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45686</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45471</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45671</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45671</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>45611</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45548</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45411</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45314</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45000</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45737</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45834</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45604</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>44931</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45180</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45673</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45380</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45321</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44848</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44812</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45266</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>45121</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44462</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45679</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>44851</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45266</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45317</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45309</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45471</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44946</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45477</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44979</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45678</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44918</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45671</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45415</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45722</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44342</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45407</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45303</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45666</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44943</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44729</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45204</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45089</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45624</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>45688</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45301</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45301</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45301</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44467</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45401</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44494</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45238</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45301</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44210</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44133</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45011</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45135</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45244</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44467</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44195</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45336</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45253</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44848</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45121</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45782</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45678</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>44175</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>44994</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44848</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>44343</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45803.34567129629</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45700</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44825</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45611</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45813</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45201</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45604</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>44734</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45194</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44314</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45089</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>44631</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45371</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45302</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45688</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45371</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44342</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44336</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>44368</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44867</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44361</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>44697</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44935</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44437</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45232</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>44904</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44641</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44230</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44935</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44498</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45103</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44138</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44294</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44334</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44278</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44309</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>44158</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44426</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>44244</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44278</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44426</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>44820</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44393</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44650</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>44512</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44484</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44082.63233796296</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>44239</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44330</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44449</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44755</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44218</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44610</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44683</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44488</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44399</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44433</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44426</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44449</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44433</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44433</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>44246</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>44426</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44383</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44546</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44409</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44286</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44176</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>44089</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44335</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44334</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44140</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44785</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44504</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44375</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44302</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44887</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44221</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44586</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44204</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>44203</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>44111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>44111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44588</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>44175</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>44564</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44383</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44298</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44447</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44511</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>44339</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>44447</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>44369</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>44447</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44330</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>44096</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44867</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44141</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44211</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44312</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44795</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44307</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44179</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44204</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44398</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44433</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44158</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44565</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>44461</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>44433</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>44433</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>44272</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44099</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>44796</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44312</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>44132</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44433</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44487</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44175</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>44163</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44154</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>44571</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>44187</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44237</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44382</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>44812</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44138</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44173</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>44846</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45331</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45196</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45161</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45362</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45187</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45190</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45159</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45730</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33417,7 +33417,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44930</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45194</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>45194</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45327</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45390</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45538</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44944</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44901</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>44463</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44847</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>44370</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>44848</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45301</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44512</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44112</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44956</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45379</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45201</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45198</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>44938</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45420</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>45093</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45686</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45117</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45086</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45454</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45468</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45306</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45258</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45035</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44977</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45474</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45338</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45471</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>44910</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45335</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45483</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>44474</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>45537</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44466</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>44937</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44845</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45797.34990740741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>44091</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44944</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45566</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>44589</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45561</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45287</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45068</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>45460</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>44912</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>44912</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45478</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45538</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>45722</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>44646</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45272</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45371</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45407.61327546297</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43866,7 +43866,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45511</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>44595</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45049</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45093</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45093</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45093</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>44669</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44125</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44447</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45531</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45216</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45321</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>44169</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45548.68</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45147</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>44573</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45245</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>44904</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45831</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44623</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>44615</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45239</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>44748</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45147</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45831</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45153</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>44180</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45077</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49300,7 +49300,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45251</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45085</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>44236</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45121</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45173</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50267,7 +50267,7 @@
         <v>45460</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45877</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45877</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45877</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>44783</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45877</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45216</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>44939</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45110</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45261</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45880</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>45272</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45265</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52691,7 +52691,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
         <v>45275</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45734.68493055556</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45245</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45366</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53514,7 +53514,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>44964</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>44433</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>44956</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45883</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45390.8940625</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45847</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>45847</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45848</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45889.67297453704</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54788,7 +54788,7 @@
         <v>45889.67606481481</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54902,7 +54902,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45847</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45889.6947337963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>44798</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45040</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45371</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45889.67436342593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>44342</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>44269</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45301</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45114</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45894.62219907407</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45894.62775462963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45278</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45894.39395833333</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>45301</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56617,7 +56617,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56731,7 +56731,7 @@
         <v>45898.62226851852</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>44935</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56902,7 +56902,7 @@
         <v>44368</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -56959,7 +56959,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>44984</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>45898.80314814814</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45477</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45140</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>44908</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57549,7 +57549,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45477</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57839,7 +57839,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57896,7 +57896,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>44152</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>44655</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58129,7 +58129,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58243,7 +58243,7 @@
         <v>44830</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58357,7 +58357,7 @@
         <v>45678</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>45730</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58528,7 +58528,7 @@
         <v>45338</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58590,7 +58590,7 @@
         <v>45483</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58647,7 +58647,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>44187</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58818,7 +58818,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58880,7 +58880,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>45201</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>44851</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>44904</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59279,7 +59279,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59507,7 +59507,7 @@
         <v>44646</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59621,7 +59621,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>44923</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>44480</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>45075</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59849,7 +59849,7 @@
         <v>44176</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>44314</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60087,7 +60087,7 @@
         <v>44218</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60144,7 +60144,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>44977</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45079</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45140</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>44987</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>44623</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60791,7 +60791,7 @@
         <v>45068</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -60967,7 +60967,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>45331</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61267,7 +61267,7 @@
         <v>44848</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>44375</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61505,7 +61505,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61567,7 +61567,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61686,7 +61686,7 @@
         <v>44971</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>45035</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61800,7 +61800,7 @@
         <v>45076</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45313</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -61971,7 +61971,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>45152</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62162,7 +62162,7 @@
         <v>44230</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>45140</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>44393</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62447,7 +62447,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62504,7 +62504,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>45089</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45191</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44848</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62804,7 +62804,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>44896</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>45089</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>44651</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63213,7 +63213,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63275,7 +63275,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>45040</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63399,7 +63399,7 @@
         <v>45104</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63456,7 +63456,7 @@
         <v>45730</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63513,7 +63513,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63627,7 +63627,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45016</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63741,7 +63741,7 @@
         <v>45021</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63798,7 +63798,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63860,7 +63860,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63917,7 +63917,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -63974,7 +63974,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64031,7 +64031,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64093,7 +64093,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64150,7 +64150,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64269,7 +64269,7 @@
         <v>44924</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64326,7 +64326,7 @@
         <v>45030</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64383,7 +64383,7 @@
         <v>44256</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>45540</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64683,7 +64683,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64740,7 +64740,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64797,7 +64797,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64854,7 +64854,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65030,7 +65030,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45483</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65149,7 +65149,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65211,7 +65211,7 @@
         <v>45036</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>45104</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65392,7 +65392,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65454,7 +65454,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65516,7 +65516,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65630,7 +65630,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65692,7 +65692,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>44484</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>44908</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -65987,7 +65987,7 @@
         <v>45068</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66044,7 +66044,7 @@
         <v>45424.98380787037</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         <v>44942</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66163,7 +66163,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66225,7 +66225,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66282,7 +66282,7 @@
         <v>44785</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66339,7 +66339,7 @@
         <v>44641</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66401,7 +66401,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66458,7 +66458,7 @@
         <v>44335</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66515,7 +66515,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66572,7 +66572,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66629,7 +66629,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66691,7 +66691,7 @@
         <v>45643</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>45012</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66862,7 +66862,7 @@
         <v>45455</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66924,7 +66924,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>45460</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67095,7 +67095,7 @@
         <v>44979</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67152,7 +67152,7 @@
         <v>44979</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67209,7 +67209,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>44783</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67385,7 +67385,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67442,7 +67442,7 @@
         <v>45414</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67499,7 +67499,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67556,7 +67556,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67675,7 +67675,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67732,7 +67732,7 @@
         <v>44960</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67789,7 +67789,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67908,7 +67908,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -67965,7 +67965,7 @@
         <v>45003</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68042,7 +68042,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68099,7 +68099,7 @@
         <v>44979</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68156,7 +68156,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68213,7 +68213,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68270,7 +68270,7 @@
         <v>44931</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68332,7 +68332,7 @@
         <v>44977</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68389,7 +68389,7 @@
         <v>44785</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68446,7 +68446,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68503,7 +68503,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68560,7 +68560,7 @@
         <v>44888</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68617,7 +68617,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68679,7 +68679,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68736,7 +68736,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68793,7 +68793,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68912,7 +68912,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -68969,7 +68969,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -69026,7 +69026,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -69083,7 +69083,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -69202,7 +69202,7 @@
         <v>45244</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44239</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>44393</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45473</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45244</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45525</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>44474</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45434</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>45530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>44284</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45671</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45468</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45551</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>44505</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>45790</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45686</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44795</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45638</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45604</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>44539</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44497</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45237</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45551</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45473</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45686</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44994</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45677</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44935</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45335</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44120</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>45204</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45608</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>45908.65443287037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45691</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45473</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45505</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45475</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45671</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44931</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45502</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44868</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45475</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45908.66357638889</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45730</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45363</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45722</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45232</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45435</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>45811</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45274</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44896</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44342</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44398</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45425</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45463</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45699</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45834</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45253</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45301</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44249</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44887</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45686</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45471</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45671</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45671</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45611</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45548</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>45314</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45411</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45000</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44931</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45180</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45604</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45737</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45673</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45834</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45321</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44848</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44812</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45121</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>44462</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45679</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44851</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45266</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45317</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45309</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>45471</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44946</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45477</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44979</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45678</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>44918</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44342</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45671</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45415</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45722</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45666</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44943</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44729</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>45204</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45624</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45089</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45301</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45301</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45301</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45238</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44494</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45011</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44467</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45301</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>44210</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44133</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45380</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45407</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45688</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45401</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45303</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45135</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45244</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44467</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44195</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44848</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45253</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45336</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45121</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45782</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45678</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44175</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44994</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>44848</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44343</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44825</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45700</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45611</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45813</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45194</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>44314</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45201</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45604</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>44734</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45089</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45302</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44631</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44342</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44336</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44368</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45371</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45688</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44437</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44867</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45898.62226851852</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44361</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44697</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>44935</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45908.67556712963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45303</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>45232</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44904</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44641</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44230</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44935</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44498</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45103</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44092</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44138</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44334</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44294</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44278</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44309</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44158</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44244</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44278</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44426</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44426</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44820</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44393</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44650</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44512</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44484</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44239</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44330</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44449</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>44755</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44218</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44683</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44488</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>44399</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44433</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44426</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44449</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>44433</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44433</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>44426</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44246</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44383</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>44546</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44409</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>44089</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44286</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44335</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44176</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>44334</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>44785</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44140</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>44504</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44375</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>44302</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>44887</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>44221</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44586</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44204</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>44203</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44588</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44175</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44564</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44383</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>44447</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44298</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44511</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>44339</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44447</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44447</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44096</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44312</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44369</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>44795</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>44179</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>44867</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44162</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>44141</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44211</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44158</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>44565</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>44307</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44258</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44099</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>44461</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>44433</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44433</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>44132</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44204</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>44433</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>44163</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>44154</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44796</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44433</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44487</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44187</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44846</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44237</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44756</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44812</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44138</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>44173</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45331</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45190</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45730</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>44930</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45194</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45194</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>44847</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45327</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>44370</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45196</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>44848</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45161</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44512</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45159</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>44112</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45390</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45538</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44944</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45379</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>44312</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44901</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44463</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45301</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45302</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44956</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45420</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44175</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45201</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45198</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44938</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45093</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45686</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45117</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45086</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45454</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45306</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45468</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44571</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45035</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44977</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>44910</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45258</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45338</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45474</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45471</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>44382</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45335</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45483</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44474</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>44466</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44937</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44845</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45566</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>44091</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45068</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44944</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45478</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44589</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>44646</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45561</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45287</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45460</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>44912</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>44912</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45538</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>45049</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45722</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45093</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45093</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45093</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         <v>44669</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>45272</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44125</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45511</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45147</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>44595</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44573</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45245</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44447</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45531</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45216</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45148</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>44623</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45239</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45321</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45147</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>44169</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45548.68</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45153</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>44180</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45251</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44904</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45173</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45831</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48168,7 +48168,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>44615</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45216</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48716,7 +48716,7 @@
         <v>45831</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>45110</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45261</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>44748</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45272</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45085</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>44236</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45121</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45877</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45877</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45877</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45460</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45877</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>44783</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>44956</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45366</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>44939</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45265</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52303,7 +52303,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>45275</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52474,7 +52474,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>44964</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>44433</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>44956</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52883,7 +52883,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53116,7 +53116,7 @@
         <v>44798</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>44342</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>44269</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45301</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45114</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45278</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45880</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>44984</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45477</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45301</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>45140</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54442,7 +54442,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54618,7 +54618,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54675,7 +54675,7 @@
         <v>44655</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>44935</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -55017,7 +55017,7 @@
         <v>44830</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45678</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45730</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45483</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>44187</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45201</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         <v>44851</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55877,7 +55877,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55934,7 +55934,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55991,7 +55991,7 @@
         <v>44368</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>44923</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>45075</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         <v>44314</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>44218</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56457,7 +56457,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56514,7 +56514,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>44977</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>45068</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56809,7 +56809,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>45331</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>44848</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57228,7 +57228,7 @@
         <v>44375</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57466,7 +57466,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57523,7 +57523,7 @@
         <v>44971</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45035</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57637,7 +57637,7 @@
         <v>45076</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57694,7 +57694,7 @@
         <v>44908</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>45033</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45477</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>45313</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -58041,7 +58041,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>45152</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>45140</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>44393</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58579,7 +58579,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58636,7 +58636,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58693,7 +58693,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58864,7 +58864,7 @@
         <v>44152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45089</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>45191</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -59040,7 +59040,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -59097,7 +59097,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59449,7 +59449,7 @@
         <v>45883</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59506,7 +59506,7 @@
         <v>45089</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59563,7 +59563,7 @@
         <v>44651</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>45338</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59806,7 +59806,7 @@
         <v>45847</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         <v>45847</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45848</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59977,7 +59977,7 @@
         <v>45889.67297453704</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45889.67606481481</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45847</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>45889.6947337963</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60490,7 +60490,7 @@
         <v>45371</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60547,7 +60547,7 @@
         <v>45889.67436342593</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60604,7 +60604,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60661,7 +60661,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45016</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60775,7 +60775,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>44904</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60889,7 +60889,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -61060,7 +61060,7 @@
         <v>44646</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>44480</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61231,7 +61231,7 @@
         <v>45894.62219907407</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61288,7 +61288,7 @@
         <v>45894.62775462963</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61345,7 +61345,7 @@
         <v>44176</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61402,7 +61402,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>45894.39395833333</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61516,7 +61516,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61573,7 +61573,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45079</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61744,7 +61744,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61801,7 +61801,7 @@
         <v>45140</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61858,7 +61858,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61915,7 +61915,7 @@
         <v>44987</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>44623</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -62034,7 +62034,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45898.80314814814</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62272,7 +62272,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62334,7 +62334,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>44230</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62562,7 +62562,7 @@
         <v>44848</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62624,7 +62624,7 @@
         <v>45903.54821759259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62681,7 +62681,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62795,7 +62795,7 @@
         <v>44896</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -63028,7 +63028,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>45040</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63147,7 +63147,7 @@
         <v>45908.62329861111</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63209,7 +63209,7 @@
         <v>45104</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>44977</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63323,7 +63323,7 @@
         <v>45730</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63380,7 +63380,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>45021</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63494,7 +63494,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63556,7 +63556,7 @@
         <v>45371</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63613,7 +63613,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>45362</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63841,7 +63841,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -64017,7 +64017,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>44924</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45030</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64193,7 +64193,7 @@
         <v>44256</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64250,7 +64250,7 @@
         <v>45912.32259259259</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64307,7 +64307,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64369,7 +64369,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64431,7 +64431,7 @@
         <v>45540</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64550,7 +64550,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64607,7 +64607,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64664,7 +64664,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64778,7 +64778,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64835,7 +64835,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64959,7 +64959,7 @@
         <v>45483</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45036</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65135,7 +65135,7 @@
         <v>45104</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65321,7 +65321,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65383,7 +65383,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65497,7 +65497,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65559,7 +65559,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65616,7 +65616,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65678,7 +65678,7 @@
         <v>44484</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65735,7 +65735,7 @@
         <v>44908</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65792,7 +65792,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>45068</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>44942</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65968,7 +65968,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -66030,7 +66030,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66087,7 +66087,7 @@
         <v>44785</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>44641</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>44335</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66434,7 +66434,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66496,7 +66496,7 @@
         <v>45643</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66553,7 +66553,7 @@
         <v>45012</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66610,7 +66610,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66667,7 +66667,7 @@
         <v>45455</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66786,7 +66786,7 @@
         <v>45460</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66900,7 +66900,7 @@
         <v>44979</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66957,7 +66957,7 @@
         <v>44979</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -67014,7 +67014,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67076,7 +67076,7 @@
         <v>44783</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67133,7 +67133,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67190,7 +67190,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67247,7 +67247,7 @@
         <v>45414</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67423,7 +67423,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67480,7 +67480,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67537,7 +67537,7 @@
         <v>44960</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67594,7 +67594,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67656,7 +67656,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67770,7 +67770,7 @@
         <v>45003</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67847,7 +67847,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67904,7 +67904,7 @@
         <v>44979</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67961,7 +67961,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -68018,7 +68018,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68075,7 +68075,7 @@
         <v>44931</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68137,7 +68137,7 @@
         <v>44785</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68194,7 +68194,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68251,7 +68251,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68308,7 +68308,7 @@
         <v>44888</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68365,7 +68365,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68427,7 +68427,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68484,7 +68484,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68541,7 +68541,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68598,7 +68598,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68717,7 +68717,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68774,7 +68774,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68831,7 +68831,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68888,7 +68888,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>45244</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>44239</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>44393</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45473</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45244</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45525</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>44474</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45434</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>45530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>44284</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45671</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45468</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45551</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>44505</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>45790</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45686</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44795</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45638</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45604</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>44539</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>44497</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45237</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45551</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45473</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45686</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44994</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45677</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44935</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45335</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>44120</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>45204</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45608</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>45908.65443287037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45691</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45473</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45505</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45475</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45671</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44931</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45502</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44868</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45475</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45908.66357638889</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45730</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45363</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45722</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45232</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45435</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>45811</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45274</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44896</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44342</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44398</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45425</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45463</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45699</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45834</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45253</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45301</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>44249</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44887</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45686</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45471</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45671</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45671</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45611</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45548</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>45314</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45411</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45000</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44931</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45180</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45604</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45737</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45673</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45834</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45321</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44848</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44812</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45121</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>44462</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45679</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44851</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45266</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45317</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45309</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>45471</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44946</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45477</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44979</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45678</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>44918</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44342</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45671</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45415</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45722</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45666</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44943</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44729</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>45204</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45624</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45089</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45301</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45301</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45840.59291666667</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45301</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45238</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44494</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45011</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44467</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45301</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>44210</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44133</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45380</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45407</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45688</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45401</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45303</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45135</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45244</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44467</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44195</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44848</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45253</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45336</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45121</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45782</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45678</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44175</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44994</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45475</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>44848</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44343</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44825</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45700</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45611</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45813</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45194</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>44314</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45201</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45604</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>44734</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45089</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45302</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44631</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44342</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44336</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44368</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45371</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45688</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44437</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44867</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45371</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45898.62226851852</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>44361</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44697</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>44935</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45908.67556712963</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45303</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>45232</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44904</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44641</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44230</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44935</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44498</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45103</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44092</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44138</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44334</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44294</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44278</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44309</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44158</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44244</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44278</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44426</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44426</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44820</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44393</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44650</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>44512</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44484</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>44239</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>44330</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44449</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>44755</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44218</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44683</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44488</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>44399</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44433</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44426</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44449</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>44433</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44433</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>44426</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44246</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44383</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>44546</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44409</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>44089</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44286</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44335</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44176</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>44334</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>44785</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44140</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>44504</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44375</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>44302</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>44887</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>44221</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44586</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44204</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>44203</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44588</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44175</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44564</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44383</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>44447</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44298</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44511</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>44339</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44447</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44447</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44096</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44312</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44369</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>44795</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>44179</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>44867</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44162</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>44141</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44211</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44158</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>44565</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>44307</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44258</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44099</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>44461</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>44433</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44433</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>44132</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44204</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>44433</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>44163</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>44154</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44796</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44433</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44487</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44187</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44846</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44237</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44756</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44812</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44138</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>44173</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45331</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45763.67365740741</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45190</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45730</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>44930</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45194</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45194</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>44847</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45327</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>44370</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45196</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>44848</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45161</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44512</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45159</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>44112</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45390</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45538</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44944</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45379</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>44312</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44901</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44463</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45301</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45302</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44956</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45420</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44175</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45201</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45198</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45754.6719212963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44938</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45093</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45686</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45117</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45086</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>45454</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45306</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45468</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44571</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45035</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44977</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>44910</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44621</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45258</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45338</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45719.38739583334</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45474</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45471</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>44382</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45790.65793981482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45335</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45537</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45483</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44474</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>44466</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>44937</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44845</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45566</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>44091</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45068</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44944</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45478</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44589</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>44646</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45561</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45287</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45460</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>44912</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>44912</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45538</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>45049</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45722</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45093</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45093</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45093</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         <v>44669</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>45272</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>44125</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45511</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45147</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>44595</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45754.66733796296</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44573</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45245</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44447</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45531</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45216</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45148</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>44623</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45239</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45321</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45147</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>44169</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45548.68</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45153</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>44180</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45251</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44904</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45173</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45831</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48168,7 +48168,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>44615</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45216</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48716,7 +48716,7 @@
         <v>45831</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>45110</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45261</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>44748</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45272</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45085</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>44236</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45121</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45877</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45877</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45877</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45460</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45877</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>44783</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>44956</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45366</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>44939</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45265</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52303,7 +52303,7 @@
         <v>45643.63751157407</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>45275</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52474,7 +52474,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>44964</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>44433</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>44956</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -52883,7 +52883,7 @@
         <v>45040</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53116,7 +53116,7 @@
         <v>44798</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>44342</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>44269</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45301</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45114</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45278</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45880</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>44984</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45477</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45301</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>45140</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54442,7 +54442,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54618,7 +54618,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54675,7 +54675,7 @@
         <v>44655</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>44935</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -55017,7 +55017,7 @@
         <v>44830</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45678</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45842.47616898148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45730</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45483</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>44187</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45201</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         <v>44851</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -55877,7 +55877,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -55934,7 +55934,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -55991,7 +55991,7 @@
         <v>44368</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56105,7 +56105,7 @@
         <v>44923</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>45075</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         <v>44314</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>44218</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56457,7 +56457,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56514,7 +56514,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>44977</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>45068</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56809,7 +56809,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>45331</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>44848</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57228,7 +57228,7 @@
         <v>44375</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57466,7 +57466,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57523,7 +57523,7 @@
         <v>44971</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45035</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57637,7 +57637,7 @@
         <v>45076</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57694,7 +57694,7 @@
         <v>44908</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>45033</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45477</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>45313</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -58041,7 +58041,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>45152</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>45140</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>44393</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58579,7 +58579,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58636,7 +58636,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58693,7 +58693,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -58864,7 +58864,7 @@
         <v>44152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45089</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>45191</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -59040,7 +59040,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -59097,7 +59097,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59278,7 +59278,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59449,7 +59449,7 @@
         <v>45883</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59506,7 +59506,7 @@
         <v>45089</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59563,7 +59563,7 @@
         <v>44651</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>45338</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59806,7 +59806,7 @@
         <v>45847</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         <v>45847</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45848</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -59977,7 +59977,7 @@
         <v>45889.67297453704</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45889.67606481481</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45847</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>45889.6947337963</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60490,7 +60490,7 @@
         <v>45371</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60547,7 +60547,7 @@
         <v>45889.67436342593</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60604,7 +60604,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60661,7 +60661,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45016</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60775,7 +60775,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>44904</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -60889,7 +60889,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -61060,7 +61060,7 @@
         <v>44646</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>44480</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61231,7 +61231,7 @@
         <v>45894.62219907407</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61288,7 +61288,7 @@
         <v>45894.62775462963</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61345,7 +61345,7 @@
         <v>44176</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61402,7 +61402,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>45894.39395833333</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61516,7 +61516,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61573,7 +61573,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45079</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61744,7 +61744,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61801,7 +61801,7 @@
         <v>45140</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -61858,7 +61858,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -61915,7 +61915,7 @@
         <v>44987</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>44623</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -62034,7 +62034,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45898.80314814814</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62272,7 +62272,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62334,7 +62334,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>44230</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62562,7 +62562,7 @@
         <v>44848</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62624,7 +62624,7 @@
         <v>45903.54821759259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62681,7 +62681,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62795,7 +62795,7 @@
         <v>44896</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -63028,7 +63028,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>45040</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63147,7 +63147,7 @@
         <v>45908.62329861111</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63209,7 +63209,7 @@
         <v>45104</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>44977</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63323,7 +63323,7 @@
         <v>45730</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63380,7 +63380,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>45021</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63494,7 +63494,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63556,7 +63556,7 @@
         <v>45371</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63613,7 +63613,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>45362</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -63841,7 +63841,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -64017,7 +64017,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>44924</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45030</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64193,7 +64193,7 @@
         <v>44256</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64250,7 +64250,7 @@
         <v>45912.32259259259</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64307,7 +64307,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64369,7 +64369,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64431,7 +64431,7 @@
         <v>45540</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64550,7 +64550,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64607,7 +64607,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64664,7 +64664,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64778,7 +64778,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -64835,7 +64835,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -64959,7 +64959,7 @@
         <v>45483</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45036</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65135,7 +65135,7 @@
         <v>45104</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65321,7 +65321,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65383,7 +65383,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65497,7 +65497,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65559,7 +65559,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65616,7 +65616,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65678,7 +65678,7 @@
         <v>44484</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65735,7 +65735,7 @@
         <v>44908</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65792,7 +65792,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>45068</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>44942</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -65968,7 +65968,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -66030,7 +66030,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66087,7 +66087,7 @@
         <v>44785</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>44641</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>44335</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66434,7 +66434,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66496,7 +66496,7 @@
         <v>45643</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66553,7 +66553,7 @@
         <v>45012</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66610,7 +66610,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66667,7 +66667,7 @@
         <v>45455</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66786,7 +66786,7 @@
         <v>45460</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -66900,7 +66900,7 @@
         <v>44979</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -66957,7 +66957,7 @@
         <v>44979</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -67014,7 +67014,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67076,7 +67076,7 @@
         <v>44783</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67133,7 +67133,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67190,7 +67190,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67247,7 +67247,7 @@
         <v>45414</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67423,7 +67423,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67480,7 +67480,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67537,7 +67537,7 @@
         <v>44960</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67594,7 +67594,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67656,7 +67656,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67770,7 +67770,7 @@
         <v>45003</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67847,7 +67847,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -67904,7 +67904,7 @@
         <v>44979</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -67961,7 +67961,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -68018,7 +68018,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68075,7 +68075,7 @@
         <v>44931</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68137,7 +68137,7 @@
         <v>44785</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68194,7 +68194,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68251,7 +68251,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68308,7 +68308,7 @@
         <v>44888</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68365,7 +68365,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68427,7 +68427,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68484,7 +68484,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68541,7 +68541,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68598,7 +68598,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68717,7 +68717,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68774,7 +68774,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -68831,7 +68831,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -68888,7 +68888,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>45244</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45112</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>45877</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44239</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>44393</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45473</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>44284</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45525</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45244</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44474</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45908.66357638889</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45530</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>45434</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45671</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45473</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45468</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45551</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>44505</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45790</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45638</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44795</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45604</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45686</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>44539</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45551</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44497</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45335</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45677</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44994</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45237</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>45473</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44935</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45204</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44120</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45608</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>45908.65443287037</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45691</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>45686</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45505</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>45635</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45730</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45671</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45475</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>44868</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44931</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>45502</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>45475</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>45473</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>44342</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>45811</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45435</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>45274</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44398</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45363</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45232</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44896</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45253</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45463</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45699</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>45301</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45877</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>45834</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45722</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>44249</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44931</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44887</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45548</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45673</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>45411</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45000</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45671</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>45671</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45471</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45604</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45737</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45611</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45180</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45314</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45834</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45686</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44494</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45301</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45266</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45471</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>44979</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>45309</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>45671</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>45415</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>44462</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45266</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>44342</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45204</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45317</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44918</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44210</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45301</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>44848</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44729</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44133</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45666</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44943</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45121</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45244</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44851</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45135</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45477</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44946</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44467</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45301</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45321</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45407</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45380</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45624</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45303</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45678</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45238</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44812</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45011</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45401</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45301</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45679</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>45722</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45688</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44467</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44195</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44825</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45103</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45782</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45121</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44904</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>44336</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44734</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>44697</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>44994</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>44175</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44498</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45611</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44361</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45336</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>44437</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>44314</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44342</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45813</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>44343</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45475</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45194</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45604</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>45302</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>44935</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44230</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>44631</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45201</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45371</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>44848</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44368</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45253</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45371</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44935</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45232</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45908.67556712963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44867</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44641</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44848</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45898.62226851852</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45303</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45917.46385416666</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45089</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45918.46114583333</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45700</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45678</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45688</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44138</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44294</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44334</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44278</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44158</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44309</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44244</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44278</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>44426</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>44820</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>44512</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44393</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44650</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44484</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>44239</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>44330</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>44449</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>44755</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44218</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44488</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44683</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44399</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44433</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44426</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44449</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44433</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>44433</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>44246</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>44426</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44383</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>44546</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>44409</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44286</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>44335</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44176</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44334</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44785</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44140</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44504</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44375</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>44369</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44302</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44221</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44887</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44586</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44203</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44204</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44111</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44111</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44588</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>44175</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44564</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>44383</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>44447</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>44298</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>44511</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44339</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>44369</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44447</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>44867</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44141</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>44211</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>44447</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>44307</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44795</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>44179</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44204</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>44162</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44433</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44158</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>44565</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>44461</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>44433</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44433</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44258</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>44272</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44796</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>44312</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>44433</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44487</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44312</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>44175</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44571</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44237</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44812</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44138</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>44382</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>44173</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44756</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45376.41653935185</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45251</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44433</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45706.8156712963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45301.51439814815</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45301.51950231481</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44956</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45701.46835648148</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>45068</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>45194</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>45194</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45754.46086805555</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45525.49710648148</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45012</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45777.50200231482</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45021</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45478</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45140</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44468.47153935185</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45551.35216435185</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45033</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45278</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45783.45644675926</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45782.61456018518</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45783.45325231482</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>45211.5790625</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45722.47424768518</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45538</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>44169</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>44928.44431712963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45740.44686342592</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45265</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45784.6615625</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>45476</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>44474</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44994.58689814815</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45604.54060185186</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45771.65724537037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45338</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44480</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44970</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45566.48361111111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>44939</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45079</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45338</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>45342.38787037037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44937</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>45379</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>44132</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>45191</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44930</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45093</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45093</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45093</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45625.33342592593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45709.38065972222</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45190</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45621.82230324074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>44621</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>45114</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44623</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>44163</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>44314</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>44830</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45036.70626157407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>44154</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45272</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45790.67273148148</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45790.39267361111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45790.39622685185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>44187</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45678</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44783</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45793.44484953704</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45793.42939814815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45198</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45237.75578703704</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45240.34900462963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45793.65996527778</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45240.44670138889</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45390</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>44901</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45671.62141203704</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45596.69706018519</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45790.65489583334</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45148</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45309.61756944445</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45484.52023148148</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45474</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>44846</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45140</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45086</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45335</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45261</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45483</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45170.59288194445</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45170.59443287037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>45121</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44112</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45244</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>45617.85399305556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45749.72953703703</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45702.39331018519</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45548.68</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45561</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45799.45109953704</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45511</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>44942</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>44910</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45706.65895833333</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45393.47158564815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45287</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>44447</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45152</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45148.84875</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44956.72383101852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44973.65422453704</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45460</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44466</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45804.43547453704</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45804.443125</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45245</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>44845</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45133.59230324074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45807.67447916666</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45807.6794212963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45807.66685185185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45807.67638888889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45807.68232638889</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44977.40112268519</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>44931</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45622.54515046296</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>45366</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45485.46388888889</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45621.83300925926</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45621.83461805555</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45677.67003472222</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45677.68149305556</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45245</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>44912</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45810.35262731482</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>44370</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>44977</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45813.32667824074</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>44988.66966435185</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45460</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>45460</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45147</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44910.48520833333</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>45817.57395833333</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>45817.56891203704</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45817.57153935185</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45818.44662037037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45817.81831018518</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45771.30550925926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45331</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45110</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45819.91342592592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>44375</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45531</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>44595</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45196.55392361111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45671.45357638889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45477</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>44904</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>44269</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45236.4803587963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45376.43302083333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45239</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>44902.80462962963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45040</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45160.40577546296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45420</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45678.60493055556</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45068</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45226.43667824074</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>44901.36292824074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45673.69037037037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45196.50065972222</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>44180</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45702.39491898148</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45635.72293981481</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45301</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>45075</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45468</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47879,7 +47879,7 @@
         <v>45003</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45764.43959490741</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45036</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45085</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45553.61355324074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45104</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45089</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>44811.46958333333</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44484</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45825.50804398148</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45671.45521990741</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>44960</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48836,7 +48836,7 @@
         <v>45755.60236111111</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45755.60278935185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>44722.35611111111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45566</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49064,7 +49064,7 @@
         <v>44785</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>45540</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>44573</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>44908</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45468.35030092593</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45468.35390046296</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45236.82902777778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>44125</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>44896</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45201</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45201.68075231482</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45483</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50514,7 +50514,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50576,7 +50576,7 @@
         <v>44615</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50633,7 +50633,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>44938</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50866,7 +50866,7 @@
         <v>44944</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>45336.62131944444</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>44785.72373842593</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>45477</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45714.61418981481</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>45035</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>44256</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51446,7 +51446,7 @@
         <v>45477.55280092593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45714.61543981481</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51622,7 +51622,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51679,7 +51679,7 @@
         <v>44623</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51865,7 +51865,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>45159</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -51979,7 +51979,7 @@
         <v>45694.37447916667</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -52036,7 +52036,7 @@
         <v>45196</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45274.46324074074</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>45331</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>45471</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45104</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45147</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>44335</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45477.36993055556</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52770,7 +52770,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -52951,7 +52951,7 @@
         <v>44944</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>45117</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>45369.39894675926</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -53122,7 +53122,7 @@
         <v>45160.67251157408</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>44236</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>44984</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>44924</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>45159.47940972223</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>44908</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>44552.43644675926</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>45076.02563657407</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -53645,7 +53645,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45831</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -53759,7 +53759,7 @@
         <v>45754.44952546297</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>45831</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45831.65177083333</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45831.53775462963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45477.61552083334</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>45477.62924768519</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>45831.63174768518</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>45831.65712962963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>45196.55849537037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -54416,7 +54416,7 @@
         <v>45201</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>45240.43778935185</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -54530,7 +54530,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         <v>44977</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -54649,7 +54649,7 @@
         <v>45258</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>44635.68771990741</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -54763,7 +54763,7 @@
         <v>44152</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -54820,7 +54820,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -54882,7 +54882,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>44230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -54996,7 +54996,7 @@
         <v>44798</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>44669</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -55110,7 +55110,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45454</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>44847</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>45553.61098379629</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45680.50885416667</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -55566,7 +55566,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>45833.67266203704</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>45833.72505787037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45833.48370370371</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45834.65864583333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45793.36922453704</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45834.5984375</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -56109,7 +56109,7 @@
         <v>45834.58306712963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>45321</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45089</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45834.62629629629</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45835.40452546296</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -56595,7 +56595,7 @@
         <v>45216</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45040</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45093</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>44923</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45838.25818287037</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45839.46924768519</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -57175,7 +57175,7 @@
         <v>45838.4546875</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>45233.65532407408</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>44646</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>44655</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>44912</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45842.48217592593</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45842.59581018519</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45842.62152777778</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45845.58966435185</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>44393</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45790.65615740741</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45842.61626157408</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45030</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45842.59880787037</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45842.61993055556</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45842.62488425926</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45621.38190972222</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -58278,7 +58278,7 @@
         <v>45621.38459490741</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>45301</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>45068</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>45272</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45407.62733796296</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45842.63288194445</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45104.49659722222</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>44987</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>45845.57983796296</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45730</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>44848</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45076</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45845.57701388889</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45847</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45847</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45889.67606481481</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45889.67436342593</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45889.6947337963</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45846.59813657407</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45889.67297453704</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45611.49178240741</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>44187</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>45089.41912037037</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -59800,7 +59800,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>45847</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45847.50152777778</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>44368</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45846.334375</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45848</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45049.566875</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -60427,7 +60427,7 @@
         <v>45848.32959490741</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -60484,7 +60484,7 @@
         <v>45371</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45849.54420138889</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -60655,7 +60655,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -60712,7 +60712,7 @@
         <v>45719.46681712963</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -60769,7 +60769,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -60826,7 +60826,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -60883,7 +60883,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>45894.62775462963</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -60997,7 +60997,7 @@
         <v>45740.45964120371</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>45035</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45894.39395833333</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45894.62219907407</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>44979</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>44979</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -61463,7 +61463,7 @@
         <v>45301</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -61520,7 +61520,7 @@
         <v>44971</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -61577,7 +61577,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>45216</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>45140</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>44651</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -61929,7 +61929,7 @@
         <v>45253</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -61986,7 +61986,7 @@
         <v>45523.49450231482</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -62043,7 +62043,7 @@
         <v>44646</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>45643</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>44785</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -62214,7 +62214,7 @@
         <v>45898.80314814814</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -62271,7 +62271,7 @@
         <v>44848</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>45714.60927083333</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -62509,7 +62509,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -62566,7 +62566,7 @@
         <v>45302</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>45264.8162037037</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45538</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45903.54821759259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -62856,7 +62856,7 @@
         <v>45049</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>44979</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -62970,7 +62970,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -63084,7 +63084,7 @@
         <v>44785.74811342593</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -63141,7 +63141,7 @@
         <v>44904</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>45740.45425925926</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45740.45748842593</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>44342</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45730</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -63607,7 +63607,7 @@
         <v>45330.80729166666</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45908.62329861111</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -63840,7 +63840,7 @@
         <v>45161</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -63897,7 +63897,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -63954,7 +63954,7 @@
         <v>45414</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -64011,7 +64011,7 @@
         <v>45313</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -64068,7 +64068,7 @@
         <v>44977</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -64125,7 +64125,7 @@
         <v>45371</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -64239,7 +64239,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -64296,7 +64296,7 @@
         <v>45722.46953703704</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>45644.46804398148</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45740.42978009259</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45740.43222222223</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>44980.52182870371</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -64596,7 +64596,7 @@
         <v>44463</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -64653,7 +64653,7 @@
         <v>45016</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>45624.38690972222</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -64767,7 +64767,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -64824,7 +64824,7 @@
         <v>44756.62649305556</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -64881,7 +64881,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -64943,7 +64943,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -65000,7 +65000,7 @@
         <v>44589</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -65062,7 +65062,7 @@
         <v>44851</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -65119,7 +65119,7 @@
         <v>44783</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -65176,7 +65176,7 @@
         <v>45691.47354166667</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -65295,7 +65295,7 @@
         <v>44888</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -65352,7 +65352,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -65409,7 +65409,7 @@
         <v>44956</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -65523,7 +65523,7 @@
         <v>44748</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -65585,7 +65585,7 @@
         <v>45754.4621412037</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -65647,7 +65647,7 @@
         <v>44512</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>45912.32259259259</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -65781,7 +65781,7 @@
         <v>45630.65180555556</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -65838,7 +65838,7 @@
         <v>45483</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -65895,7 +65895,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -65952,7 +65952,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -66014,7 +66014,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -66071,7 +66071,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -66133,7 +66133,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -66190,7 +66190,7 @@
         <v>45723.63655092593</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -66247,7 +66247,7 @@
         <v>45723.63827546296</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>44964</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -66361,7 +66361,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -66418,7 +66418,7 @@
         <v>45275</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -66475,7 +66475,7 @@
         <v>45153</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -66532,7 +66532,7 @@
         <v>44641</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -66594,7 +66594,7 @@
         <v>45237.76106481482</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>44820.44106481481</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -66708,7 +66708,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -66765,7 +66765,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -66822,7 +66822,7 @@
         <v>44848</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -66884,7 +66884,7 @@
         <v>45327</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -66941,7 +66941,7 @@
         <v>45148.84990740741</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -67003,7 +67003,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -67065,7 +67065,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -67122,7 +67122,7 @@
         <v>44176</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -67179,7 +67179,7 @@
         <v>45077</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -67236,7 +67236,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -67293,7 +67293,7 @@
         <v>45306.53221064815</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -67350,7 +67350,7 @@
         <v>45306</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>45173</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -67526,7 +67526,7 @@
         <v>45916.62190972222</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -67583,7 +67583,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>45877</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -67697,7 +67697,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -67821,7 +67821,7 @@
         <v>45918.44545138889</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -67878,7 +67878,7 @@
         <v>45918.44818287037</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -67935,7 +67935,7 @@
         <v>44218</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -67992,7 +67992,7 @@
         <v>45877</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>45918.45793981481</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -68126,7 +68126,7 @@
         <v>45918.64869212963</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -68183,7 +68183,7 @@
         <v>45537</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -68245,7 +68245,7 @@
         <v>45621.82039351852</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -68307,7 +68307,7 @@
         <v>44371.63414351852</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -68364,7 +68364,7 @@
         <v>45371.4966087963</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -68421,7 +68421,7 @@
         <v>45918.44344907408</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -68478,7 +68478,7 @@
         <v>45918.31287037037</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -68535,7 +68535,7 @@
         <v>44935</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -68592,7 +68592,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -68649,7 +68649,7 @@
         <v>45923.65804398148</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -68706,7 +68706,7 @@
         <v>45880</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -68763,7 +68763,7 @@
         <v>45686</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -68840,7 +68840,7 @@
         <v>45722</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -68897,7 +68897,7 @@
         <v>45883</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -68954,7 +68954,7 @@
         <v>45362</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -69011,7 +69011,7 @@
         <v>45924.63246527778</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -69068,7 +69068,7 @@
         <v>45924.63511574074</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -69125,7 +69125,7 @@
         <v>45924.63733796297</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -567,7 +567,7 @@
         <v>44902</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         <v>44896</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44883</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45908.66357638889</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>45112</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>45877</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45643.59024305556</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>44239</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>44393</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45726.63050925926</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45473</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45244</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44474</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45434</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>44284</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45525</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45468</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>45740.46803240741</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45671</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>45473</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45848.30584490741</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45908.65443287037</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45604</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>45638</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45755.51844907407</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45686</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>45551</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44505</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45790</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>45807.68491898148</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44795</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>44539</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44497</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>45848.32703703704</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>45204</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45608</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45473</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44935</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44994</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44120</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45686</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45691</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45335</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45551</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45677</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45475</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45617.38247685185</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>44931</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45635</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45475</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45730</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44868</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45473</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>45505</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45671</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45593.55731481482</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45502</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45853.47163194444</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>45425</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45848.33202546297</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45463</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>45699</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45533.45459490741</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>45301</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45253</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45877</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44342</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45681.62086805556</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44398</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45722</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45834</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45560.54571759259</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>45799.4640625</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45435</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45811</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45363</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44896</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45232</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45274</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44249</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45860.36769675926</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45737</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45866.56780092593</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>45411</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45355.74270833333</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45673</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45000</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45611</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>45834</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>45590.49690972222</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45475.35597222222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45548</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44931</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>45180</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>45777.6084837963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45635.71747685185</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44887</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>45671</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45671</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45471</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45783.45474537037</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45604</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>45314</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>44285.66680555556</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45321</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45376.41797453703</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45378.31111111111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>44848</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44467</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44494</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44943</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>44851</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45266</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45317</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45380</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45309</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>45407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45841.69072916666</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>45471</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44904.55646990741</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45908.67556712963</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45301</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44946</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>44210</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45477</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44133</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44979</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44918</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45089</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45303</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45678</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45362.63960648148</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45401</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45740.44130787037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45722</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45135</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45688</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45679</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45238</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45244</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45610.44008101852</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45530.54184027778</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45266</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45560.54628472222</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45740.47012731482</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45011</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45355.73453703704</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45121</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44462</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45671</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45777.60479166666</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45415</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45539.51238425926</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44547.90868055556</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45555.31039351852</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44342</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45846.34083333334</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45666</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45740.44487268518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44729</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45754.46833333333</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45204</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45624</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45301</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45301</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45301</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44195</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>44848</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>44467</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44368</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45201</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44734</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>44867</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44175</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45729.68322916667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45475</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45266.27928240741</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45714.60472222222</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45870.513125</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44848</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>44343</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44361</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45622.5916087963</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>44697</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45089</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45303</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44631</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>44935</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45917.46385416666</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45918.46114583333</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45898.62226851852</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45140.52086805556</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45678</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>45232</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45611</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44342</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45722.46649305556</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>44336</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>44904</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45740.44363425926</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>44641</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>44230</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45688</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45604.5640625</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>44935</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45740.47480324074</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44498</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45714.61153935185</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45625.4175</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45754.46579861111</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>45754.46709490741</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45740.45232638889</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45253</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45760.85842592592</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45782</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45783.45039351852</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>44437</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45336</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>44994</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45791.44415509259</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>45791.45371527778</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45121</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45791.45887731481</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45799.50620370371</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45807.55402777778</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45133.59306712963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45133.59490740741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45671.44059027778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45187.53707175926</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45813</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45604</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45831.63834490741</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45740.43934027778</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45842.61306712963</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45371</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>44825</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45845.58349537037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45845.5819675926</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45845.64383101852</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45621.8252199074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45371</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45715.61996527778</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45700.38141203704</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45194</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45681.34420138889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>44314</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45681.43706018518</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45302</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45527.60524305556</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>44210.65167824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>44243.6503125</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>44138</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>44294</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>44334</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>44278</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>44309</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>44158</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>44426</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44294.68079861111</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>44244</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>44400.63459490741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>44278</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>44582.5518287037</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>44683.64341435185</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44426</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44873.67061342593</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44820</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>44393</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>44650</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44512</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>44168.64150462963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44449.37518518518</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44484</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44274.39513888889</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44239</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44201.62629629629</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>44330</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44335.88846064815</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44399.49815972222</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44449</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44755</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44218</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44683</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44488</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>44399</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>44433</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>44426</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>44449</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>44460.68069444445</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44433</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>44433</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>44246</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>44426</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44621.90621527778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44383</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44546</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44851.49836805555</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>44409</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>44286</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44176</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44335</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44876.43712962963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44334</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>44673.48178240741</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44174.32638888889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>44785</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44140</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44851.50041666667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44504</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44285.67078703704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44375</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44274.71607638889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44369</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44387.67591435185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>44302</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44887</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>44221</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44586</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44204</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44861.60849537037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44203</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44111</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44111</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44266.55212962963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44588</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44175</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44564</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44383</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44447</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44298</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>44511</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>44339</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>44501.45256944445</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>44447</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44825.41880787037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>44368.90879629629</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44480.82696759259</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>44179</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>44201.63928240741</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>44162</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>44130.63965277778</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>44158</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44565</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>44272</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>44454.63494212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>44454.63644675926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>44498.65975694444</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>44132</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44258</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44461</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44480.82778935185</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>44433</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44433</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>44312</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44163</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44154</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>44175</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>44621.91652777778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44848.59880787037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>44571</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>44187</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>44796</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44433</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>44487</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>44379.45400462963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44379.4646875</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44400.63810185185</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44382</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>44595.63739583334</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44846</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44565.63162037037</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44368.91321759259</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>44188.47537037037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>44237</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45621.39938657408</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45187</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>45190</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45730</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>45194</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45194</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45327</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>44812</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>44138</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>44173</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45202.59584490741</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>44756</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>45331</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>44312</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>44306.31681712963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44298.49047453704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44335.88916666667</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>44320.5672337963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45355.73599537037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>44930</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>44369</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>45379.44450231481</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45036.70215277778</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>44545.56285879629</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>44867</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>44847</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>44447</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>44370</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>44848</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>44141</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33387,7 +33387,7 @@
         <v>44211</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45391.44385416667</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>44307</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -33563,7 +33563,7 @@
         <v>44512</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44112</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44285.66303240741</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44795</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45754.45739583333</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45754.4644675926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44454.63141203704</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44204</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44433</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44825.40943287037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45379</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>45301</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45302</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45817.57549768518</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45460.44732638889</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45463.58467592593</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45894.39395833333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45420</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44369.56576388889</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44973.64606481481</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45604.55837962963</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45301.54230324074</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45301.54412037037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44509.56346064815</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45637.54589120371</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45631.51325231481</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44935</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44973.88759259259</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44368</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>45853.43320601852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45589.49168981481</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45853.31940972222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45442.58048611111</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44901.36453703704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>45391.4450462963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45391.44789351852</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45671.61953703704</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45211.49424768519</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44908</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45033</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44904.48152777777</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>44904.52560185185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>44904</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45117</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45371.53141203704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45477</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45086</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45898.80314814814</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45454</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45468</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45391.44885416667</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45525.59111111111</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45260.40186342593</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44916.62880787037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44152</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44970</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45533.620625</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>45240.65173611111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45576.69753472223</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44893.5862037037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44615</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>44861.45876157407</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45338</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>44973.88452546296</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45016.41767361111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44848.8315625</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>44748</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>45256.85211805555</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45489.60528935185</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45903.54821759259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45258</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45791.40225694444</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45401.63736111111</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45770.60177083333</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45783.45542824074</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45474</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45737.85231481482</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45471</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45512.63465277778</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45512.63642361111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>44904</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>44904.51767361111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>44904.53423611111</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>45525.57712962963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45825.57524305556</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>44881.68282407407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45077</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>44994.35707175926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>45537.90300925926</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>45174.72416666667</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>44646</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45908.62329861111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44960.73170138889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>44480</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44977</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44176</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>44218.60984953704</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>44970.37244212963</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45371</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45301.53930555555</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45483</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>44474</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>44946.61086805556</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>45085</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45079</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45140</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>44987</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>44623</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44916.90010416666</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45621.39516203704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>44236</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45530.40025462963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>44963.37194444444</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>44278.41052083333</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45121</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45671.45061342593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45256.85107638889</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44466</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44937</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44845</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45912.32259259259</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45343.80621527778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45460</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>44944</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45629.43973379629</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>44564.62540509259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>44564.62763888889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>44783</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45204.5684837963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44956</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45635.67120370371</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>44589</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45359.87989583334</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>44230</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>44946.60753472222</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45775.55954861111</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45873.5591087963</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>44904.53858796296</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45916.62190972222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45873.56483796296</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45740.42127314815</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45740.42738425926</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44848</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45460</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45764.4417824074</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44939</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45535.67180555555</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45321.58569444445</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44896</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45275</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45621.39081018518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>44462.80449074074</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>44462.806875</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45265</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45147.59408564815</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>44912</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44912</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45918.64869212963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45918.44344907408</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45918.45793981481</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45673.68859953704</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45040</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45104</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45625.41949074074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>44487.50277777778</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45730</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>44776.74908564815</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>44468.48255787037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>45918.31287037037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -43516,7 +43516,7 @@
         <v>44867.62262731481</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45245</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45918.44545138889</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>45918.44818287037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45538</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>45000.43240740741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>44720.70361111111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>44964</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>45021</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45740.39541666667</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45880</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>44449.46614583334</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>44433</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>44956</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45222.55333333334</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>44532.48237268518</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>44964.61592592593</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>45877</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>45016.39048611111</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>45877</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>44539.37123842593</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>45391.44646990741</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45272</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>44924</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45677.68357638889</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44964.35730324074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45642.61109953704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45030</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
         <v>45924.63733796297</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>44256</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45702.3918287037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>44798</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45282.27841435185</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45282.28041666667</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45540</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>44342</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45643.60487268519</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45677.62704861111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>44977.46979166667</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>44977.56759259259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45924.63246527778</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45924.63511574074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45742.57653935185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45374.97038194445</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45681.44637731482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45754.45234953704</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45754.45355324074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45691.50069444445</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45483</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45923.65804398148</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45160.67677083334</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45036</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45511</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45596.69846064815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45104</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>44269</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>44595</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45160.60331018519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45264.81439814815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45264.81490740741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45362</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45085.43271990741</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47145,7 +47145,7 @@
         <v>44672.47105324074</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>45485.46721064814</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>45701.46581018518</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>45204.56195601852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>45671.61569444444</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>45610.53413194444</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>45147.59215277778</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>44929.51619212963</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45391.45087962963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>44484</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>44908</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>45701.46288194445</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45529.64638888889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45621.39759259259</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45068</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>44447</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>44942</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45666.65664351852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45722.4630787037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45160.66336805555</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>45531</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>45622.58350694444</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>44785</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>44984</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>44984.64269675926</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45117.72543981481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45216</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>44641</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45722.52284722222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45477</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45140</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45358.59056712963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45035.53497685185</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45379.4459375</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45321</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>44335</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>45253</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>44169</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45548.68</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45147.60667824074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45022.41916666667</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -49542,7 +49542,7 @@
         <v>45643</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45012</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45590.69163194444</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45455</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>45485.46129629629</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45460</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>44989.64261574074</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45705.32234953704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>44979</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>44979</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45035.54475694444</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45448.39869212963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>44783</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>44728.45674768519</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>44655</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45686</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45883</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45722</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>44383</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>44795.48444444445</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45677.67711805556</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>44830</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45678</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45730</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>45202.42667824074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45631.34590277778</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45483</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>45414</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>45743.64482638889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -51230,7 +51230,7 @@
         <v>45148.85041666667</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -51292,7 +51292,7 @@
         <v>44589.67060185185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>44187</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>45722.53427083333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>45740.43785879629</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45567.68774305555</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45240.45217592592</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>44960</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45201</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45468.70357638889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>44979.65015046296</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45215.59601851852</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -51929,7 +51929,7 @@
         <v>45003</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -52006,7 +52006,7 @@
         <v>44298.47847222222</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>44851</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>44979</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45300.55188657407</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45215.65043981482</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         <v>45747.40813657407</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>44532.56175925926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>44923.46215277778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -52462,7 +52462,7 @@
         <v>44923</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>44931</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -52581,7 +52581,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>44785</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -52695,7 +52695,7 @@
         <v>45553.61674768518</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>44314</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -52814